--- a/output/publication/tariff_impacts_results_20260401.xlsx
+++ b/output/publication/tariff_impacts_results_20260401.xlsx
@@ -5530,13 +5530,13 @@
         <v>30</v>
       </c>
       <c r="C238" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D238" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E238" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F238" s="7" t="n">
         <v>3123.773412637</v>
@@ -5550,13 +5550,13 @@
         <v>30</v>
       </c>
       <c r="C239" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D239" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E239" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F239" s="7" t="n">
         <v>3123.773412637</v>
@@ -5570,13 +5570,13 @@
         <v>30</v>
       </c>
       <c r="C240" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D240" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E240" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F240" s="7" t="n">
         <v>3123.773412637</v>
@@ -5590,13 +5590,13 @@
         <v>30</v>
       </c>
       <c r="C241" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D241" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E241" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F241" s="7" t="n">
         <v>3123.773412637</v>
@@ -5610,13 +5610,13 @@
         <v>30</v>
       </c>
       <c r="C242" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D242" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E242" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F242" s="7" t="n">
         <v>3123.773412637</v>
@@ -5630,13 +5630,13 @@
         <v>30</v>
       </c>
       <c r="C243" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D243" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E243" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F243" s="7" t="n">
         <v>3123.773412637</v>
@@ -5650,13 +5650,13 @@
         <v>30</v>
       </c>
       <c r="C244" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D244" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E244" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F244" s="7" t="n">
         <v>3123.773412637</v>
@@ -5670,13 +5670,13 @@
         <v>30</v>
       </c>
       <c r="C245" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D245" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E245" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F245" s="7" t="n">
         <v>3123.773412637</v>
@@ -5690,13 +5690,13 @@
         <v>31</v>
       </c>
       <c r="C246" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D246" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E246" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F246" s="7" t="n">
         <v>3123.773412637</v>
@@ -5710,13 +5710,13 @@
         <v>31</v>
       </c>
       <c r="C247" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D247" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E247" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F247" s="7" t="n">
         <v>3123.773412637</v>
@@ -5730,13 +5730,13 @@
         <v>31</v>
       </c>
       <c r="C248" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D248" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E248" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F248" s="7" t="n">
         <v>3123.773412637</v>
@@ -5750,13 +5750,13 @@
         <v>31</v>
       </c>
       <c r="C249" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D249" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E249" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F249" s="7" t="n">
         <v>3123.773412637</v>
@@ -5770,13 +5770,13 @@
         <v>31</v>
       </c>
       <c r="C250" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D250" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E250" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F250" s="7" t="n">
         <v>3123.773412637</v>
@@ -5790,13 +5790,13 @@
         <v>31</v>
       </c>
       <c r="C251" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D251" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E251" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F251" s="7" t="n">
         <v>3123.773412637</v>
@@ -5810,13 +5810,13 @@
         <v>32</v>
       </c>
       <c r="C252" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D252" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E252" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F252" s="7" t="n">
         <v>3123.773412637</v>
@@ -5830,13 +5830,13 @@
         <v>32</v>
       </c>
       <c r="C253" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D253" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E253" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F253" s="7" t="n">
         <v>3123.773412637</v>
@@ -5850,13 +5850,13 @@
         <v>32</v>
       </c>
       <c r="C254" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D254" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E254" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F254" s="7" t="n">
         <v>3123.773412637</v>
@@ -5870,13 +5870,13 @@
         <v>32</v>
       </c>
       <c r="C255" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D255" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E255" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F255" s="7" t="n">
         <v>3123.773412637</v>
@@ -5890,13 +5890,13 @@
         <v>32</v>
       </c>
       <c r="C256" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D256" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E256" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F256" s="7" t="n">
         <v>3123.773412637</v>
@@ -5910,13 +5910,13 @@
         <v>32</v>
       </c>
       <c r="C257" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D257" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E257" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F257" s="7" t="n">
         <v>3123.773412637</v>
@@ -5930,13 +5930,13 @@
         <v>32</v>
       </c>
       <c r="C258" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D258" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E258" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F258" s="7" t="n">
         <v>3123.773412637</v>
@@ -5950,13 +5950,13 @@
         <v>32</v>
       </c>
       <c r="C259" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D259" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E259" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F259" s="7" t="n">
         <v>3123.773412637</v>
@@ -5970,13 +5970,13 @@
         <v>32</v>
       </c>
       <c r="C260" s="7" t="n">
-        <v>0.156965210547705</v>
+        <v>0.160495243246783</v>
       </c>
       <c r="D260" s="7" t="n">
-        <v>0.146484911473566</v>
+        <v>0.149934900025347</v>
       </c>
       <c r="E260" s="7" t="n">
-        <v>2265.508907812</v>
+        <v>2289.609192107</v>
       </c>
       <c r="F260" s="7" t="n">
         <v>3123.773412637</v>
@@ -5990,13 +5990,13 @@
         <v>33</v>
       </c>
       <c r="C261" s="7" t="n">
-        <v>0.154987290476626</v>
+        <v>0.158516358352216</v>
       </c>
       <c r="D261" s="7" t="n">
-        <v>0.144506918702297</v>
+        <v>0.14795594243059</v>
       </c>
       <c r="E261" s="7" t="n">
-        <v>2265.717247798</v>
+        <v>2289.613200467</v>
       </c>
       <c r="F261" s="7" t="n">
         <v>3123.773412637</v>
@@ -6010,13 +6010,13 @@
         <v>33</v>
       </c>
       <c r="C262" s="7" t="n">
-        <v>0.154987290476626</v>
+        <v>0.158516358352216</v>
       </c>
       <c r="D262" s="7" t="n">
-        <v>0.144506918702297</v>
+        <v>0.14795594243059</v>
       </c>
       <c r="E262" s="7" t="n">
-        <v>2265.717247798</v>
+        <v>2289.613200467</v>
       </c>
       <c r="F262" s="7" t="n">
         <v>3123.773412637</v>
@@ -6030,13 +6030,13 @@
         <v>33</v>
       </c>
       <c r="C263" s="7" t="n">
-        <v>0.154987290476626</v>
+        <v>0.158516358352216</v>
       </c>
       <c r="D263" s="7" t="n">
-        <v>0.144506918702297</v>
+        <v>0.14795594243059</v>
       </c>
       <c r="E263" s="7" t="n">
-        <v>2265.717247798</v>
+        <v>2289.613200467</v>
       </c>
       <c r="F263" s="7" t="n">
         <v>3123.773412637</v>
@@ -6050,13 +6050,13 @@
         <v>33</v>
       </c>
       <c r="C264" s="7" t="n">
-        <v>0.154987290476626</v>
+        <v>0.158516358352216</v>
       </c>
       <c r="D264" s="7" t="n">
-        <v>0.144506918702297</v>
+        <v>0.14795594243059</v>
       </c>
       <c r="E264" s="7" t="n">
-        <v>2265.717247798</v>
+        <v>2289.613200467</v>
       </c>
       <c r="F264" s="7" t="n">
         <v>3123.773412637</v>
@@ -6070,13 +6070,13 @@
         <v>33</v>
       </c>
       <c r="C265" s="7" t="n">
-        <v>0.154987290476626</v>
+        <v>0.158516358352216</v>
       </c>
       <c r="D265" s="7" t="n">
-        <v>0.144506918702297</v>
+        <v>0.14795594243059</v>
       </c>
       <c r="E265" s="7" t="n">
-        <v>2265.717247798</v>
+        <v>2289.613200467</v>
       </c>
       <c r="F265" s="7" t="n">
         <v>3123.773412637</v>
@@ -6090,13 +6090,13 @@
         <v>33</v>
       </c>
       <c r="C266" s="7" t="n">
-        <v>0.154987290476626</v>
+        <v>0.158516358352216</v>
       </c>
       <c r="D266" s="7" t="n">
-        <v>0.144506918702297</v>
+        <v>0.14795594243059</v>
       </c>
       <c r="E266" s="7" t="n">
-        <v>2265.717247798</v>
+        <v>2289.613200467</v>
       </c>
       <c r="F266" s="7" t="n">
         <v>3123.773412637</v>
@@ -6110,13 +6110,13 @@
         <v>33</v>
       </c>
       <c r="C267" s="7" t="n">
-        <v>0.154987290476626</v>
+        <v>0.158516358352216</v>
       </c>
       <c r="D267" s="7" t="n">
-        <v>0.144506918702297</v>
+        <v>0.14795594243059</v>
       </c>
       <c r="E267" s="7" t="n">
-        <v>2265.717247798</v>
+        <v>2289.613200467</v>
       </c>
       <c r="F267" s="7" t="n">
         <v>3123.773412637</v>
@@ -6130,13 +6130,13 @@
         <v>34</v>
       </c>
       <c r="C268" s="7" t="n">
-        <v>0.152432950741588</v>
+        <v>0.155962661125355</v>
       </c>
       <c r="D268" s="7" t="n">
-        <v>0.141952650822793</v>
+        <v>0.145402317059263</v>
       </c>
       <c r="E268" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F268" s="7" t="n">
         <v>3123.773412637</v>
@@ -6150,13 +6150,13 @@
         <v>34</v>
       </c>
       <c r="C269" s="7" t="n">
-        <v>0.152432950741588</v>
+        <v>0.155962661125355</v>
       </c>
       <c r="D269" s="7" t="n">
-        <v>0.141952650822793</v>
+        <v>0.145402317059263</v>
       </c>
       <c r="E269" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F269" s="7" t="n">
         <v>3123.773412637</v>
@@ -6170,13 +6170,13 @@
         <v>34</v>
       </c>
       <c r="C270" s="7" t="n">
-        <v>0.152432950741588</v>
+        <v>0.155962661125355</v>
       </c>
       <c r="D270" s="7" t="n">
-        <v>0.141952650822793</v>
+        <v>0.145402317059263</v>
       </c>
       <c r="E270" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F270" s="7" t="n">
         <v>3123.773412637</v>
@@ -6190,13 +6190,13 @@
         <v>34</v>
       </c>
       <c r="C271" s="7" t="n">
-        <v>0.152432950741588</v>
+        <v>0.155962661125355</v>
       </c>
       <c r="D271" s="7" t="n">
-        <v>0.141952650822793</v>
+        <v>0.145402317059263</v>
       </c>
       <c r="E271" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F271" s="7" t="n">
         <v>3123.773412637</v>
@@ -6210,13 +6210,13 @@
         <v>34</v>
       </c>
       <c r="C272" s="7" t="n">
-        <v>0.152432950741588</v>
+        <v>0.155962661125355</v>
       </c>
       <c r="D272" s="7" t="n">
-        <v>0.141952650822793</v>
+        <v>0.145402317059263</v>
       </c>
       <c r="E272" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F272" s="7" t="n">
         <v>3123.773412637</v>
@@ -6230,13 +6230,13 @@
         <v>34</v>
       </c>
       <c r="C273" s="7" t="n">
-        <v>0.152432950741588</v>
+        <v>0.155962661125355</v>
       </c>
       <c r="D273" s="7" t="n">
-        <v>0.141952650822793</v>
+        <v>0.145402317059263</v>
       </c>
       <c r="E273" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F273" s="7" t="n">
         <v>3123.773412637</v>
@@ -6250,13 +6250,13 @@
         <v>34</v>
       </c>
       <c r="C274" s="7" t="n">
-        <v>0.152432950741588</v>
+        <v>0.155962661125355</v>
       </c>
       <c r="D274" s="7" t="n">
-        <v>0.141952650822793</v>
+        <v>0.145402317059263</v>
       </c>
       <c r="E274" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F274" s="7" t="n">
         <v>3123.773412637</v>
@@ -6270,13 +6270,13 @@
         <v>35</v>
       </c>
       <c r="C275" s="7" t="n">
-        <v>0.152920100537803</v>
+        <v>0.15644981092157</v>
       </c>
       <c r="D275" s="7" t="n">
-        <v>0.142439800619009</v>
+        <v>0.145889466855478</v>
       </c>
       <c r="E275" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F275" s="7" t="n">
         <v>3123.773412637</v>
@@ -6290,13 +6290,13 @@
         <v>35</v>
       </c>
       <c r="C276" s="7" t="n">
-        <v>0.152920100537803</v>
+        <v>0.15644981092157</v>
       </c>
       <c r="D276" s="7" t="n">
-        <v>0.142439800619009</v>
+        <v>0.145889466855478</v>
       </c>
       <c r="E276" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F276" s="7" t="n">
         <v>3123.773412637</v>
@@ -6310,13 +6310,13 @@
         <v>35</v>
       </c>
       <c r="C277" s="7" t="n">
-        <v>0.152920100537803</v>
+        <v>0.15644981092157</v>
       </c>
       <c r="D277" s="7" t="n">
-        <v>0.142439800619009</v>
+        <v>0.145889466855478</v>
       </c>
       <c r="E277" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F277" s="7" t="n">
         <v>3123.773412637</v>
@@ -6330,13 +6330,13 @@
         <v>35</v>
       </c>
       <c r="C278" s="7" t="n">
-        <v>0.152920100537803</v>
+        <v>0.15644981092157</v>
       </c>
       <c r="D278" s="7" t="n">
-        <v>0.142439800619009</v>
+        <v>0.145889466855478</v>
       </c>
       <c r="E278" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F278" s="7" t="n">
         <v>3123.773412637</v>
@@ -6350,13 +6350,13 @@
         <v>35</v>
       </c>
       <c r="C279" s="7" t="n">
-        <v>0.152920100537803</v>
+        <v>0.15644981092157</v>
       </c>
       <c r="D279" s="7" t="n">
-        <v>0.142439800619009</v>
+        <v>0.145889466855478</v>
       </c>
       <c r="E279" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F279" s="7" t="n">
         <v>3123.773412637</v>
@@ -6370,13 +6370,13 @@
         <v>35</v>
       </c>
       <c r="C280" s="7" t="n">
-        <v>0.152920100537803</v>
+        <v>0.15644981092157</v>
       </c>
       <c r="D280" s="7" t="n">
-        <v>0.142439800619009</v>
+        <v>0.145889466855478</v>
       </c>
       <c r="E280" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F280" s="7" t="n">
         <v>3123.773412637</v>
@@ -6390,13 +6390,13 @@
         <v>35</v>
       </c>
       <c r="C281" s="7" t="n">
-        <v>0.152920100537803</v>
+        <v>0.15644981092157</v>
       </c>
       <c r="D281" s="7" t="n">
-        <v>0.142439800619009</v>
+        <v>0.145889466855478</v>
       </c>
       <c r="E281" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F281" s="7" t="n">
         <v>3123.773412637</v>
@@ -6410,13 +6410,13 @@
         <v>35</v>
       </c>
       <c r="C282" s="7" t="n">
-        <v>0.152920100537803</v>
+        <v>0.15644981092157</v>
       </c>
       <c r="D282" s="7" t="n">
-        <v>0.142439800619009</v>
+        <v>0.145889466855478</v>
       </c>
       <c r="E282" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F282" s="7" t="n">
         <v>3123.773412637</v>
@@ -6430,13 +6430,13 @@
         <v>35</v>
       </c>
       <c r="C283" s="7" t="n">
-        <v>0.152920100537803</v>
+        <v>0.15644981092157</v>
       </c>
       <c r="D283" s="7" t="n">
-        <v>0.142439800619009</v>
+        <v>0.145889466855478</v>
       </c>
       <c r="E283" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F283" s="7" t="n">
         <v>3123.773412637</v>
@@ -6450,13 +6450,13 @@
         <v>35</v>
       </c>
       <c r="C284" s="7" t="n">
-        <v>0.152920100537803</v>
+        <v>0.15644981092157</v>
       </c>
       <c r="D284" s="7" t="n">
-        <v>0.142439800619009</v>
+        <v>0.145889466855478</v>
       </c>
       <c r="E284" s="7" t="n">
-        <v>2265.552973576</v>
+        <v>2289.609241541</v>
       </c>
       <c r="F284" s="7" t="n">
         <v>3123.773412637</v>
@@ -6470,13 +6470,13 @@
         <v>36</v>
       </c>
       <c r="C285" s="7" t="n">
-        <v>0.154033640239277</v>
+        <v>0.157728670162122</v>
       </c>
       <c r="D285" s="7" t="n">
-        <v>0.143548330881646</v>
+        <v>0.147163703212593</v>
       </c>
       <c r="E285" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F285" s="7" t="n">
         <v>3123.773412637</v>
@@ -6490,13 +6490,13 @@
         <v>36</v>
       </c>
       <c r="C286" s="7" t="n">
-        <v>0.154033640239277</v>
+        <v>0.157728670162122</v>
       </c>
       <c r="D286" s="7" t="n">
-        <v>0.143548330881646</v>
+        <v>0.147163703212593</v>
       </c>
       <c r="E286" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F286" s="7" t="n">
         <v>3123.773412637</v>
@@ -6510,13 +6510,13 @@
         <v>36</v>
       </c>
       <c r="C287" s="7" t="n">
-        <v>0.154033640239277</v>
+        <v>0.157728670162122</v>
       </c>
       <c r="D287" s="7" t="n">
-        <v>0.143548330881646</v>
+        <v>0.147163703212593</v>
       </c>
       <c r="E287" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F287" s="7" t="n">
         <v>3123.773412637</v>
@@ -6530,13 +6530,13 @@
         <v>36</v>
       </c>
       <c r="C288" s="7" t="n">
-        <v>0.154033640239277</v>
+        <v>0.157728670162122</v>
       </c>
       <c r="D288" s="7" t="n">
-        <v>0.143548330881646</v>
+        <v>0.147163703212593</v>
       </c>
       <c r="E288" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F288" s="7" t="n">
         <v>3123.773412637</v>
@@ -6550,13 +6550,13 @@
         <v>36</v>
       </c>
       <c r="C289" s="7" t="n">
-        <v>0.154033640239277</v>
+        <v>0.157728670162122</v>
       </c>
       <c r="D289" s="7" t="n">
-        <v>0.143548330881646</v>
+        <v>0.147163703212593</v>
       </c>
       <c r="E289" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F289" s="7" t="n">
         <v>3123.773412637</v>
@@ -6570,13 +6570,13 @@
         <v>36</v>
       </c>
       <c r="C290" s="7" t="n">
-        <v>0.154033640239277</v>
+        <v>0.157728670162122</v>
       </c>
       <c r="D290" s="7" t="n">
-        <v>0.143548330881646</v>
+        <v>0.147163703212593</v>
       </c>
       <c r="E290" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F290" s="7" t="n">
         <v>3123.773412637</v>
@@ -6590,13 +6590,13 @@
         <v>36</v>
       </c>
       <c r="C291" s="7" t="n">
-        <v>0.154033640239277</v>
+        <v>0.157728670162122</v>
       </c>
       <c r="D291" s="7" t="n">
-        <v>0.143548330881646</v>
+        <v>0.147163703212593</v>
       </c>
       <c r="E291" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F291" s="7" t="n">
         <v>3123.773412637</v>
@@ -6610,13 +6610,13 @@
         <v>36</v>
       </c>
       <c r="C292" s="7" t="n">
-        <v>0.154033640239277</v>
+        <v>0.157728670162122</v>
       </c>
       <c r="D292" s="7" t="n">
-        <v>0.143548330881646</v>
+        <v>0.147163703212593</v>
       </c>
       <c r="E292" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F292" s="7" t="n">
         <v>3123.773412637</v>
@@ -6630,13 +6630,13 @@
         <v>36</v>
       </c>
       <c r="C293" s="7" t="n">
-        <v>0.154033640239277</v>
+        <v>0.157728670162122</v>
       </c>
       <c r="D293" s="7" t="n">
-        <v>0.143548330881646</v>
+        <v>0.147163703212593</v>
       </c>
       <c r="E293" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F293" s="7" t="n">
         <v>3123.773412637</v>
@@ -6650,13 +6650,13 @@
         <v>37</v>
       </c>
       <c r="C294" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D294" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E294" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F294" s="7" t="n">
         <v>3123.773412637</v>
@@ -6670,13 +6670,13 @@
         <v>37</v>
       </c>
       <c r="C295" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D295" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E295" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F295" s="7" t="n">
         <v>3123.773412637</v>
@@ -6690,13 +6690,13 @@
         <v>37</v>
       </c>
       <c r="C296" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D296" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E296" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F296" s="7" t="n">
         <v>3123.773412637</v>
@@ -6710,13 +6710,13 @@
         <v>37</v>
       </c>
       <c r="C297" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D297" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E297" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F297" s="7" t="n">
         <v>3123.773412637</v>
@@ -6730,13 +6730,13 @@
         <v>37</v>
       </c>
       <c r="C298" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D298" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E298" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F298" s="7" t="n">
         <v>3123.773412637</v>
@@ -6750,13 +6750,13 @@
         <v>37</v>
       </c>
       <c r="C299" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D299" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E299" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F299" s="7" t="n">
         <v>3123.773412637</v>
@@ -6770,13 +6770,13 @@
         <v>37</v>
       </c>
       <c r="C300" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D300" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E300" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F300" s="7" t="n">
         <v>3123.773412637</v>
@@ -6790,13 +6790,13 @@
         <v>38</v>
       </c>
       <c r="C301" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D301" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E301" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F301" s="7" t="n">
         <v>3123.773412637</v>
@@ -6810,13 +6810,13 @@
         <v>38</v>
       </c>
       <c r="C302" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D302" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E302" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F302" s="7" t="n">
         <v>3123.773412637</v>
@@ -6830,13 +6830,13 @@
         <v>38</v>
       </c>
       <c r="C303" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D303" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E303" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F303" s="7" t="n">
         <v>3123.773412637</v>
@@ -6850,13 +6850,13 @@
         <v>38</v>
       </c>
       <c r="C304" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D304" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E304" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F304" s="7" t="n">
         <v>3123.773412637</v>
@@ -6870,13 +6870,13 @@
         <v>38</v>
       </c>
       <c r="C305" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D305" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E305" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F305" s="7" t="n">
         <v>3123.773412637</v>
@@ -6890,13 +6890,13 @@
         <v>38</v>
       </c>
       <c r="C306" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D306" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E306" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F306" s="7" t="n">
         <v>3123.773412637</v>
@@ -6910,13 +6910,13 @@
         <v>38</v>
       </c>
       <c r="C307" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D307" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E307" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F307" s="7" t="n">
         <v>3123.773412637</v>
@@ -6930,13 +6930,13 @@
         <v>38</v>
       </c>
       <c r="C308" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D308" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E308" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F308" s="7" t="n">
         <v>3123.773412637</v>
@@ -6950,13 +6950,13 @@
         <v>38</v>
       </c>
       <c r="C309" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D309" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E309" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F309" s="7" t="n">
         <v>3123.773412637</v>
@@ -6970,13 +6970,13 @@
         <v>39</v>
       </c>
       <c r="C310" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D310" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E310" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F310" s="7" t="n">
         <v>3123.773412637</v>
@@ -6990,13 +6990,13 @@
         <v>39</v>
       </c>
       <c r="C311" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D311" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E311" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F311" s="7" t="n">
         <v>3123.773412637</v>
@@ -7010,13 +7010,13 @@
         <v>39</v>
       </c>
       <c r="C312" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D312" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E312" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F312" s="7" t="n">
         <v>3123.773412637</v>
@@ -7030,13 +7030,13 @@
         <v>39</v>
       </c>
       <c r="C313" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D313" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E313" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F313" s="7" t="n">
         <v>3123.773412637</v>
@@ -7050,13 +7050,13 @@
         <v>39</v>
       </c>
       <c r="C314" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D314" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E314" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F314" s="7" t="n">
         <v>3123.773412637</v>
@@ -7070,13 +7070,13 @@
         <v>40</v>
       </c>
       <c r="C315" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D315" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E315" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F315" s="7" t="n">
         <v>3123.773412637</v>
@@ -7090,13 +7090,13 @@
         <v>40</v>
       </c>
       <c r="C316" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D316" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E316" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F316" s="7" t="n">
         <v>3123.773412637</v>
@@ -7110,13 +7110,13 @@
         <v>40</v>
       </c>
       <c r="C317" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D317" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E317" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F317" s="7" t="n">
         <v>3123.773412637</v>
@@ -7130,13 +7130,13 @@
         <v>40</v>
       </c>
       <c r="C318" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D318" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E318" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F318" s="7" t="n">
         <v>3123.773412637</v>
@@ -7150,13 +7150,13 @@
         <v>40</v>
       </c>
       <c r="C319" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D319" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E319" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F319" s="7" t="n">
         <v>3123.773412637</v>
@@ -7170,13 +7170,13 @@
         <v>40</v>
       </c>
       <c r="C320" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D320" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E320" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F320" s="7" t="n">
         <v>3123.773412637</v>
@@ -7190,13 +7190,13 @@
         <v>40</v>
       </c>
       <c r="C321" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D321" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E321" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F321" s="7" t="n">
         <v>3123.773412637</v>
@@ -7210,13 +7210,13 @@
         <v>41</v>
       </c>
       <c r="C322" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D322" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E322" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F322" s="7" t="n">
         <v>3123.773412637</v>
@@ -7230,13 +7230,13 @@
         <v>41</v>
       </c>
       <c r="C323" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D323" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E323" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F323" s="7" t="n">
         <v>3123.773412637</v>
@@ -7250,13 +7250,13 @@
         <v>41</v>
       </c>
       <c r="C324" s="7" t="n">
-        <v>0.140728223392544</v>
+        <v>0.144423353771873</v>
       </c>
       <c r="D324" s="7" t="n">
-        <v>0.130242914034913</v>
+        <v>0.133858386822343</v>
       </c>
       <c r="E324" s="7" t="n">
-        <v>2265.724902877</v>
+        <v>2289.720099535</v>
       </c>
       <c r="F324" s="7" t="n">
         <v>3123.773412637</v>
@@ -7270,13 +7270,13 @@
         <v>42</v>
       </c>
       <c r="C325" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D325" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E325" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F325" s="7" t="n">
         <v>3123.773412637</v>
@@ -7290,13 +7290,13 @@
         <v>42</v>
       </c>
       <c r="C326" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D326" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E326" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F326" s="7" t="n">
         <v>3123.773412637</v>
@@ -7310,13 +7310,13 @@
         <v>42</v>
       </c>
       <c r="C327" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D327" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E327" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F327" s="7" t="n">
         <v>3123.773412637</v>
@@ -7330,13 +7330,13 @@
         <v>42</v>
       </c>
       <c r="C328" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D328" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E328" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F328" s="7" t="n">
         <v>3123.773412637</v>
@@ -7350,13 +7350,13 @@
         <v>42</v>
       </c>
       <c r="C329" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D329" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E329" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F329" s="7" t="n">
         <v>3123.773412637</v>
@@ -7370,13 +7370,13 @@
         <v>42</v>
       </c>
       <c r="C330" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D330" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E330" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F330" s="7" t="n">
         <v>3123.773412637</v>
@@ -7390,13 +7390,13 @@
         <v>42</v>
       </c>
       <c r="C331" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D331" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E331" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F331" s="7" t="n">
         <v>3123.773412637</v>
@@ -7410,13 +7410,13 @@
         <v>42</v>
       </c>
       <c r="C332" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D332" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E332" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F332" s="7" t="n">
         <v>3123.773412637</v>
@@ -7430,13 +7430,13 @@
         <v>42</v>
       </c>
       <c r="C333" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D333" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E333" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F333" s="7" t="n">
         <v>3123.773412637</v>
@@ -7450,13 +7450,13 @@
         <v>42</v>
       </c>
       <c r="C334" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D334" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E334" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F334" s="7" t="n">
         <v>3123.773412637</v>
@@ -7470,13 +7470,13 @@
         <v>42</v>
       </c>
       <c r="C335" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D335" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E335" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F335" s="7" t="n">
         <v>3123.773412637</v>
@@ -7490,13 +7490,13 @@
         <v>42</v>
       </c>
       <c r="C336" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D336" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E336" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F336" s="7" t="n">
         <v>3123.773412637</v>
@@ -7510,13 +7510,13 @@
         <v>42</v>
       </c>
       <c r="C337" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D337" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E337" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F337" s="7" t="n">
         <v>3123.773412637</v>
@@ -7530,13 +7530,13 @@
         <v>42</v>
       </c>
       <c r="C338" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D338" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E338" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F338" s="7" t="n">
         <v>3123.773412637</v>
@@ -7550,13 +7550,13 @@
         <v>42</v>
       </c>
       <c r="C339" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D339" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E339" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F339" s="7" t="n">
         <v>3123.773412637</v>
@@ -7570,13 +7570,13 @@
         <v>42</v>
       </c>
       <c r="C340" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D340" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E340" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F340" s="7" t="n">
         <v>3123.773412637</v>
@@ -7590,13 +7590,13 @@
         <v>42</v>
       </c>
       <c r="C341" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D341" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E341" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F341" s="7" t="n">
         <v>3123.773412637</v>
@@ -7610,13 +7610,13 @@
         <v>42</v>
       </c>
       <c r="C342" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D342" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E342" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F342" s="7" t="n">
         <v>3123.773412637</v>
@@ -7630,13 +7630,13 @@
         <v>42</v>
       </c>
       <c r="C343" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D343" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E343" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F343" s="7" t="n">
         <v>3123.773412637</v>
@@ -7650,13 +7650,13 @@
         <v>42</v>
       </c>
       <c r="C344" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D344" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E344" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F344" s="7" t="n">
         <v>3123.773412637</v>
@@ -7670,13 +7670,13 @@
         <v>42</v>
       </c>
       <c r="C345" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D345" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E345" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F345" s="7" t="n">
         <v>3123.773412637</v>
@@ -7690,13 +7690,13 @@
         <v>42</v>
       </c>
       <c r="C346" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D346" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E346" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F346" s="7" t="n">
         <v>3123.773412637</v>
@@ -7710,13 +7710,13 @@
         <v>42</v>
       </c>
       <c r="C347" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D347" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E347" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F347" s="7" t="n">
         <v>3123.773412637</v>
@@ -7730,13 +7730,13 @@
         <v>42</v>
       </c>
       <c r="C348" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D348" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E348" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F348" s="7" t="n">
         <v>3123.773412637</v>
@@ -7750,13 +7750,13 @@
         <v>42</v>
       </c>
       <c r="C349" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D349" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E349" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F349" s="7" t="n">
         <v>3123.773412637</v>
@@ -7770,13 +7770,13 @@
         <v>42</v>
       </c>
       <c r="C350" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D350" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E350" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F350" s="7" t="n">
         <v>3123.773412637</v>
@@ -7790,13 +7790,13 @@
         <v>42</v>
       </c>
       <c r="C351" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D351" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E351" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F351" s="7" t="n">
         <v>3123.773412637</v>
@@ -7810,13 +7810,13 @@
         <v>42</v>
       </c>
       <c r="C352" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D352" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E352" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F352" s="7" t="n">
         <v>3123.773412637</v>
@@ -7830,13 +7830,13 @@
         <v>42</v>
       </c>
       <c r="C353" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D353" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E353" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F353" s="7" t="n">
         <v>3123.773412637</v>
@@ -7850,13 +7850,13 @@
         <v>42</v>
       </c>
       <c r="C354" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D354" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E354" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F354" s="7" t="n">
         <v>3123.773412637</v>
@@ -7870,13 +7870,13 @@
         <v>42</v>
       </c>
       <c r="C355" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D355" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E355" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F355" s="7" t="n">
         <v>3123.773412637</v>
@@ -7890,13 +7890,13 @@
         <v>42</v>
       </c>
       <c r="C356" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D356" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E356" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F356" s="7" t="n">
         <v>3123.773412637</v>
@@ -7910,13 +7910,13 @@
         <v>42</v>
       </c>
       <c r="C357" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D357" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E357" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F357" s="7" t="n">
         <v>3123.773412637</v>
@@ -7930,13 +7930,13 @@
         <v>42</v>
       </c>
       <c r="C358" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D358" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E358" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F358" s="7" t="n">
         <v>3123.773412637</v>
@@ -7950,13 +7950,13 @@
         <v>42</v>
       </c>
       <c r="C359" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D359" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E359" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F359" s="7" t="n">
         <v>3123.773412637</v>
@@ -7970,13 +7970,13 @@
         <v>42</v>
       </c>
       <c r="C360" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D360" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E360" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F360" s="7" t="n">
         <v>3123.773412637</v>
@@ -7990,13 +7990,13 @@
         <v>42</v>
       </c>
       <c r="C361" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D361" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E361" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F361" s="7" t="n">
         <v>3123.773412637</v>
@@ -8010,13 +8010,13 @@
         <v>42</v>
       </c>
       <c r="C362" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D362" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E362" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F362" s="7" t="n">
         <v>3123.773412637</v>
@@ -8030,13 +8030,13 @@
         <v>42</v>
       </c>
       <c r="C363" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D363" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E363" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F363" s="7" t="n">
         <v>3123.773412637</v>
@@ -8050,13 +8050,13 @@
         <v>42</v>
       </c>
       <c r="C364" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D364" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E364" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F364" s="7" t="n">
         <v>3123.773412637</v>
@@ -8070,13 +8070,13 @@
         <v>42</v>
       </c>
       <c r="C365" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D365" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E365" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F365" s="7" t="n">
         <v>3123.773412637</v>
@@ -8090,13 +8090,13 @@
         <v>42</v>
       </c>
       <c r="C366" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D366" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E366" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F366" s="7" t="n">
         <v>3123.773412637</v>
@@ -8110,13 +8110,13 @@
         <v>42</v>
       </c>
       <c r="C367" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D367" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E367" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F367" s="7" t="n">
         <v>3123.773412637</v>
@@ -8130,13 +8130,13 @@
         <v>42</v>
       </c>
       <c r="C368" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D368" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E368" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F368" s="7" t="n">
         <v>3123.773412637</v>
@@ -8150,13 +8150,13 @@
         <v>42</v>
       </c>
       <c r="C369" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D369" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E369" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F369" s="7" t="n">
         <v>3123.773412637</v>
@@ -8170,13 +8170,13 @@
         <v>42</v>
       </c>
       <c r="C370" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D370" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E370" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F370" s="7" t="n">
         <v>3123.773412637</v>
@@ -8190,13 +8190,13 @@
         <v>42</v>
       </c>
       <c r="C371" s="7" t="n">
-        <v>0.13812697866111</v>
+        <v>0.141827439184871</v>
       </c>
       <c r="D371" s="7" t="n">
-        <v>0.127642978380228</v>
+        <v>0.13126378131209</v>
       </c>
       <c r="E371" s="7" t="n">
-        <v>2265.681090829</v>
+        <v>2289.696820214</v>
       </c>
       <c r="F371" s="7" t="n">
         <v>3123.773412637</v>
@@ -8210,13 +8210,13 @@
         <v>43</v>
       </c>
       <c r="C372" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D372" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E372" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F372" s="7" t="n">
         <v>3123.773412637</v>
@@ -8230,13 +8230,13 @@
         <v>43</v>
       </c>
       <c r="C373" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D373" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E373" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F373" s="7" t="n">
         <v>3123.773412637</v>
@@ -8250,13 +8250,13 @@
         <v>43</v>
       </c>
       <c r="C374" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D374" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E374" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F374" s="7" t="n">
         <v>3123.773412637</v>
@@ -8270,13 +8270,13 @@
         <v>43</v>
       </c>
       <c r="C375" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D375" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E375" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F375" s="7" t="n">
         <v>3123.773412637</v>
@@ -8290,13 +8290,13 @@
         <v>43</v>
       </c>
       <c r="C376" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D376" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E376" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F376" s="7" t="n">
         <v>3123.773412637</v>
@@ -8310,13 +8310,13 @@
         <v>43</v>
       </c>
       <c r="C377" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D377" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E377" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F377" s="7" t="n">
         <v>3123.773412637</v>
@@ -8330,13 +8330,13 @@
         <v>43</v>
       </c>
       <c r="C378" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D378" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E378" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F378" s="7" t="n">
         <v>3123.773412637</v>
@@ -8350,13 +8350,13 @@
         <v>43</v>
       </c>
       <c r="C379" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D379" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E379" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F379" s="7" t="n">
         <v>3123.773412637</v>
@@ -8370,13 +8370,13 @@
         <v>43</v>
       </c>
       <c r="C380" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D380" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E380" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F380" s="7" t="n">
         <v>3123.773412637</v>
@@ -8390,13 +8390,13 @@
         <v>43</v>
       </c>
       <c r="C381" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D381" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E381" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F381" s="7" t="n">
         <v>3123.773412637</v>
@@ -8410,13 +8410,13 @@
         <v>43</v>
       </c>
       <c r="C382" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D382" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E382" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F382" s="7" t="n">
         <v>3123.773412637</v>
@@ -8430,13 +8430,13 @@
         <v>43</v>
       </c>
       <c r="C383" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D383" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E383" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F383" s="7" t="n">
         <v>3123.773412637</v>
@@ -8450,13 +8450,13 @@
         <v>43</v>
       </c>
       <c r="C384" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D384" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E384" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F384" s="7" t="n">
         <v>3123.773412637</v>
@@ -8470,13 +8470,13 @@
         <v>43</v>
       </c>
       <c r="C385" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D385" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E385" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F385" s="7" t="n">
         <v>3123.773412637</v>
@@ -8490,13 +8490,13 @@
         <v>43</v>
       </c>
       <c r="C386" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D386" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E386" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F386" s="7" t="n">
         <v>3123.773412637</v>
@@ -8510,13 +8510,13 @@
         <v>44</v>
       </c>
       <c r="C387" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D387" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E387" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F387" s="7" t="n">
         <v>3123.773412637</v>
@@ -8530,13 +8530,13 @@
         <v>44</v>
       </c>
       <c r="C388" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D388" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E388" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F388" s="7" t="n">
         <v>3123.773412637</v>
@@ -8550,13 +8550,13 @@
         <v>44</v>
       </c>
       <c r="C389" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D389" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E389" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F389" s="7" t="n">
         <v>3123.773412637</v>
@@ -8570,13 +8570,13 @@
         <v>44</v>
       </c>
       <c r="C390" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D390" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E390" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F390" s="7" t="n">
         <v>3123.773412637</v>
@@ -8590,13 +8590,13 @@
         <v>44</v>
       </c>
       <c r="C391" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D391" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E391" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F391" s="7" t="n">
         <v>3123.773412637</v>
@@ -8610,13 +8610,13 @@
         <v>44</v>
       </c>
       <c r="C392" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D392" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E392" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F392" s="7" t="n">
         <v>3123.773412637</v>
@@ -8630,13 +8630,13 @@
         <v>44</v>
       </c>
       <c r="C393" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D393" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E393" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F393" s="7" t="n">
         <v>3123.773412637</v>
@@ -8650,13 +8650,13 @@
         <v>44</v>
       </c>
       <c r="C394" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D394" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E394" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F394" s="7" t="n">
         <v>3123.773412637</v>
@@ -8670,13 +8670,13 @@
         <v>44</v>
       </c>
       <c r="C395" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D395" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E395" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>3123.773412637</v>
@@ -8690,13 +8690,13 @@
         <v>44</v>
       </c>
       <c r="C396" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D396" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E396" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F396" s="7" t="n">
         <v>3123.773412637</v>
@@ -8710,13 +8710,13 @@
         <v>44</v>
       </c>
       <c r="C397" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D397" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E397" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>3123.773412637</v>
@@ -8730,13 +8730,13 @@
         <v>44</v>
       </c>
       <c r="C398" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D398" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E398" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F398" s="7" t="n">
         <v>3123.773412637</v>
@@ -8750,13 +8750,13 @@
         <v>44</v>
       </c>
       <c r="C399" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D399" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E399" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F399" s="7" t="n">
         <v>3123.773412637</v>
@@ -8770,13 +8770,13 @@
         <v>44</v>
       </c>
       <c r="C400" s="7" t="n">
-        <v>0.138125848631788</v>
+        <v>0.141826403272625</v>
       </c>
       <c r="D400" s="7" t="n">
-        <v>0.127641849195563</v>
+        <v>0.131262746244501</v>
       </c>
       <c r="E400" s="7" t="n">
-        <v>2265.657557792</v>
+        <v>2289.69677078</v>
       </c>
       <c r="F400" s="7" t="n">
         <v>3123.773412637</v>
@@ -8790,13 +8790,13 @@
         <v>45</v>
       </c>
       <c r="C401" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D401" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E401" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>3123.773412637</v>
@@ -8810,13 +8810,13 @@
         <v>45</v>
       </c>
       <c r="C402" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D402" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E402" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F402" s="7" t="n">
         <v>3123.773412637</v>
@@ -8830,13 +8830,13 @@
         <v>45</v>
       </c>
       <c r="C403" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D403" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E403" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F403" s="7" t="n">
         <v>3123.773412637</v>
@@ -8850,13 +8850,13 @@
         <v>45</v>
       </c>
       <c r="C404" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D404" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E404" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F404" s="7" t="n">
         <v>3123.773412637</v>
@@ -8870,13 +8870,13 @@
         <v>45</v>
       </c>
       <c r="C405" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D405" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E405" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F405" s="7" t="n">
         <v>3123.773412637</v>
@@ -8890,13 +8890,13 @@
         <v>45</v>
       </c>
       <c r="C406" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D406" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E406" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F406" s="7" t="n">
         <v>3123.773412637</v>
@@ -8910,13 +8910,13 @@
         <v>45</v>
       </c>
       <c r="C407" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D407" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E407" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F407" s="7" t="n">
         <v>3123.773412637</v>
@@ -8930,13 +8930,13 @@
         <v>45</v>
       </c>
       <c r="C408" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D408" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E408" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F408" s="7" t="n">
         <v>3123.773412637</v>
@@ -8950,13 +8950,13 @@
         <v>45</v>
       </c>
       <c r="C409" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D409" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E409" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F409" s="7" t="n">
         <v>3123.773412637</v>
@@ -8970,13 +8970,13 @@
         <v>45</v>
       </c>
       <c r="C410" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D410" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E410" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F410" s="7" t="n">
         <v>3123.773412637</v>
@@ -8990,13 +8990,13 @@
         <v>45</v>
       </c>
       <c r="C411" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D411" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E411" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F411" s="7" t="n">
         <v>3123.773412637</v>
@@ -9010,13 +9010,13 @@
         <v>45</v>
       </c>
       <c r="C412" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D412" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E412" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F412" s="7" t="n">
         <v>3123.773412637</v>
@@ -9030,13 +9030,13 @@
         <v>45</v>
       </c>
       <c r="C413" s="7" t="n">
-        <v>0.13434987309868</v>
+        <v>0.138008071172032</v>
       </c>
       <c r="D413" s="7" t="n">
-        <v>0.124007307005666</v>
+        <v>0.127587640364631</v>
       </c>
       <c r="E413" s="7" t="n">
-        <v>2226.08932244</v>
+        <v>2249.625143851</v>
       </c>
       <c r="F413" s="7" t="n">
         <v>3123.773412637</v>
@@ -9050,13 +9050,13 @@
         <v>46</v>
       </c>
       <c r="C414" s="7" t="n">
-        <v>0.131817638762157</v>
+        <v>0.135523265247883</v>
       </c>
       <c r="D414" s="7" t="n">
-        <v>0.121475072669143</v>
+        <v>0.125102834440482</v>
       </c>
       <c r="E414" s="7" t="n">
-        <v>2226.459460679</v>
+        <v>2249.99528209</v>
       </c>
       <c r="F414" s="7" t="n">
         <v>3123.773412637</v>
@@ -9070,13 +9070,13 @@
         <v>46</v>
       </c>
       <c r="C415" s="7" t="n">
-        <v>0.131817638762157</v>
+        <v>0.135523265247883</v>
       </c>
       <c r="D415" s="7" t="n">
-        <v>0.121475072669143</v>
+        <v>0.125102834440482</v>
       </c>
       <c r="E415" s="7" t="n">
-        <v>2226.459460679</v>
+        <v>2249.99528209</v>
       </c>
       <c r="F415" s="7" t="n">
         <v>3123.773412637</v>
@@ -9090,13 +9090,13 @@
         <v>46</v>
       </c>
       <c r="C416" s="7" t="n">
-        <v>0.131817638762157</v>
+        <v>0.135523265247883</v>
       </c>
       <c r="D416" s="7" t="n">
-        <v>0.121475072669143</v>
+        <v>0.125102834440482</v>
       </c>
       <c r="E416" s="7" t="n">
-        <v>2226.459460679</v>
+        <v>2249.99528209</v>
       </c>
       <c r="F416" s="7" t="n">
         <v>3123.773412637</v>
@@ -9110,13 +9110,13 @@
         <v>46</v>
       </c>
       <c r="C417" s="7" t="n">
-        <v>0.131817638762157</v>
+        <v>0.135523265247883</v>
       </c>
       <c r="D417" s="7" t="n">
-        <v>0.121475072669143</v>
+        <v>0.125102834440482</v>
       </c>
       <c r="E417" s="7" t="n">
-        <v>2226.459460679</v>
+        <v>2249.99528209</v>
       </c>
       <c r="F417" s="7" t="n">
         <v>3123.773412637</v>
@@ -9130,13 +9130,13 @@
         <v>46</v>
       </c>
       <c r="C418" s="7" t="n">
-        <v>0.131817638762157</v>
+        <v>0.135523265247883</v>
       </c>
       <c r="D418" s="7" t="n">
-        <v>0.121475072669143</v>
+        <v>0.125102834440482</v>
       </c>
       <c r="E418" s="7" t="n">
-        <v>2226.459460679</v>
+        <v>2249.99528209</v>
       </c>
       <c r="F418" s="7" t="n">
         <v>3123.773412637</v>
@@ -9150,13 +9150,13 @@
         <v>46</v>
       </c>
       <c r="C419" s="7" t="n">
-        <v>0.131817638762157</v>
+        <v>0.135523265247883</v>
       </c>
       <c r="D419" s="7" t="n">
-        <v>0.121475072669143</v>
+        <v>0.125102834440482</v>
       </c>
       <c r="E419" s="7" t="n">
-        <v>2226.459460679</v>
+        <v>2249.99528209</v>
       </c>
       <c r="F419" s="7" t="n">
         <v>3123.773412637</v>
@@ -9170,13 +9170,13 @@
         <v>46</v>
       </c>
       <c r="C420" s="7" t="n">
-        <v>0.131817638762157</v>
+        <v>0.135523265247883</v>
       </c>
       <c r="D420" s="7" t="n">
-        <v>0.121475072669143</v>
+        <v>0.125102834440482</v>
       </c>
       <c r="E420" s="7" t="n">
-        <v>2226.459460679</v>
+        <v>2249.99528209</v>
       </c>
       <c r="F420" s="7" t="n">
         <v>3123.773412637</v>
@@ -9190,13 +9190,13 @@
         <v>46</v>
       </c>
       <c r="C421" s="7" t="n">
-        <v>0.131817638762157</v>
+        <v>0.135523265247883</v>
       </c>
       <c r="D421" s="7" t="n">
-        <v>0.121475072669143</v>
+        <v>0.125102834440482</v>
       </c>
       <c r="E421" s="7" t="n">
-        <v>2226.459460679</v>
+        <v>2249.99528209</v>
       </c>
       <c r="F421" s="7" t="n">
         <v>3123.773412637</v>
@@ -9210,10 +9210,10 @@
         <v>47</v>
       </c>
       <c r="C422" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D422" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E422" s="7" t="n">
         <v>2959.787849956</v>
@@ -9230,10 +9230,10 @@
         <v>47</v>
       </c>
       <c r="C423" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D423" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E423" s="7" t="n">
         <v>2959.787849956</v>
@@ -9250,10 +9250,10 @@
         <v>47</v>
       </c>
       <c r="C424" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D424" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E424" s="7" t="n">
         <v>2959.787849956</v>
@@ -9270,10 +9270,10 @@
         <v>47</v>
       </c>
       <c r="C425" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D425" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E425" s="7" t="n">
         <v>2959.787849956</v>
@@ -9290,10 +9290,10 @@
         <v>47</v>
       </c>
       <c r="C426" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D426" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E426" s="7" t="n">
         <v>2959.787849956</v>
@@ -9310,10 +9310,10 @@
         <v>47</v>
       </c>
       <c r="C427" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D427" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E427" s="7" t="n">
         <v>2959.787849956</v>
@@ -9330,10 +9330,10 @@
         <v>47</v>
       </c>
       <c r="C428" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D428" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E428" s="7" t="n">
         <v>2959.787849956</v>
@@ -9350,10 +9350,10 @@
         <v>47</v>
       </c>
       <c r="C429" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D429" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E429" s="7" t="n">
         <v>2959.787849956</v>
@@ -9370,10 +9370,10 @@
         <v>47</v>
       </c>
       <c r="C430" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D430" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E430" s="7" t="n">
         <v>2959.787849956</v>
@@ -9390,10 +9390,10 @@
         <v>47</v>
       </c>
       <c r="C431" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D431" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E431" s="7" t="n">
         <v>2959.787849956</v>
@@ -9410,10 +9410,10 @@
         <v>47</v>
       </c>
       <c r="C432" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D432" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E432" s="7" t="n">
         <v>2959.787849956</v>
@@ -9430,10 +9430,10 @@
         <v>47</v>
       </c>
       <c r="C433" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D433" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E433" s="7" t="n">
         <v>2959.787849956</v>
@@ -9450,10 +9450,10 @@
         <v>47</v>
       </c>
       <c r="C434" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D434" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E434" s="7" t="n">
         <v>2959.787849956</v>
@@ -9470,10 +9470,10 @@
         <v>47</v>
       </c>
       <c r="C435" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D435" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E435" s="7" t="n">
         <v>2959.787849956</v>
@@ -9490,10 +9490,10 @@
         <v>47</v>
       </c>
       <c r="C436" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D436" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E436" s="7" t="n">
         <v>2959.787849956</v>
@@ -9510,10 +9510,10 @@
         <v>47</v>
       </c>
       <c r="C437" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D437" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E437" s="7" t="n">
         <v>2959.787849956</v>
@@ -9530,10 +9530,10 @@
         <v>47</v>
       </c>
       <c r="C438" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D438" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E438" s="7" t="n">
         <v>2959.787849956</v>
@@ -9550,10 +9550,10 @@
         <v>47</v>
       </c>
       <c r="C439" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D439" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E439" s="7" t="n">
         <v>2959.787849956</v>
@@ -9570,10 +9570,10 @@
         <v>47</v>
       </c>
       <c r="C440" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D440" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E440" s="7" t="n">
         <v>2959.787849956</v>
@@ -9590,10 +9590,10 @@
         <v>47</v>
       </c>
       <c r="C441" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D441" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E441" s="7" t="n">
         <v>2959.787849956</v>
@@ -9610,10 +9610,10 @@
         <v>47</v>
       </c>
       <c r="C442" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D442" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E442" s="7" t="n">
         <v>2959.787849956</v>
@@ -9630,10 +9630,10 @@
         <v>47</v>
       </c>
       <c r="C443" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D443" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E443" s="7" t="n">
         <v>2959.787849956</v>
@@ -9650,10 +9650,10 @@
         <v>47</v>
       </c>
       <c r="C444" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D444" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E444" s="7" t="n">
         <v>2959.787849956</v>
@@ -9670,10 +9670,10 @@
         <v>47</v>
       </c>
       <c r="C445" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D445" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E445" s="7" t="n">
         <v>2959.787849956</v>
@@ -9690,10 +9690,10 @@
         <v>47</v>
       </c>
       <c r="C446" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D446" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E446" s="7" t="n">
         <v>2959.787849956</v>
@@ -9710,10 +9710,10 @@
         <v>47</v>
       </c>
       <c r="C447" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D447" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E447" s="7" t="n">
         <v>2959.787849956</v>
@@ -9730,10 +9730,10 @@
         <v>47</v>
       </c>
       <c r="C448" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D448" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E448" s="7" t="n">
         <v>2959.787849956</v>
@@ -9750,10 +9750,10 @@
         <v>47</v>
       </c>
       <c r="C449" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D449" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E449" s="7" t="n">
         <v>2959.787849956</v>
@@ -9770,10 +9770,10 @@
         <v>47</v>
       </c>
       <c r="C450" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D450" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E450" s="7" t="n">
         <v>2959.787849956</v>
@@ -9790,10 +9790,10 @@
         <v>47</v>
       </c>
       <c r="C451" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D451" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E451" s="7" t="n">
         <v>2959.787849956</v>
@@ -9810,10 +9810,10 @@
         <v>47</v>
       </c>
       <c r="C452" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D452" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E452" s="7" t="n">
         <v>2959.787849956</v>
@@ -9830,10 +9830,10 @@
         <v>47</v>
       </c>
       <c r="C453" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D453" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E453" s="7" t="n">
         <v>2959.787849956</v>
@@ -9850,10 +9850,10 @@
         <v>47</v>
       </c>
       <c r="C454" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D454" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E454" s="7" t="n">
         <v>2959.787849956</v>
@@ -9870,10 +9870,10 @@
         <v>47</v>
       </c>
       <c r="C455" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D455" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E455" s="7" t="n">
         <v>2959.787849956</v>
@@ -9890,10 +9890,10 @@
         <v>47</v>
       </c>
       <c r="C456" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D456" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E456" s="7" t="n">
         <v>2959.787849956</v>
@@ -9910,10 +9910,10 @@
         <v>47</v>
       </c>
       <c r="C457" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D457" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E457" s="7" t="n">
         <v>2959.787849956</v>
@@ -9930,10 +9930,10 @@
         <v>47</v>
       </c>
       <c r="C458" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D458" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E458" s="7" t="n">
         <v>2959.787849956</v>
@@ -9950,10 +9950,10 @@
         <v>47</v>
       </c>
       <c r="C459" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D459" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E459" s="7" t="n">
         <v>2959.787849956</v>
@@ -9970,10 +9970,10 @@
         <v>47</v>
       </c>
       <c r="C460" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D460" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E460" s="7" t="n">
         <v>2959.787849956</v>
@@ -9990,10 +9990,10 @@
         <v>47</v>
       </c>
       <c r="C461" s="7" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D461" s="7" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E461" s="7" t="n">
         <v>2959.787849956</v>
@@ -10010,10 +10010,10 @@
         <v>47</v>
       </c>
       <c r="C462" s="11" t="n">
-        <v>0.106318456053298</v>
+        <v>0.110251133521227</v>
       </c>
       <c r="D462" s="11" t="n">
-        <v>0.0945453764411408</v>
+        <v>0.0984780539090698</v>
       </c>
       <c r="E462" s="11" t="n">
         <v>2959.787849956</v>
@@ -39726,16 +39726,16 @@
         <v>30</v>
       </c>
       <c r="C238" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D238" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E238" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F238" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G238" s="7" t="n">
         <v>0</v>
@@ -39749,16 +39749,16 @@
         <v>30</v>
       </c>
       <c r="C239" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D239" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E239" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F239" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G239" s="7" t="n">
         <v>0</v>
@@ -39772,16 +39772,16 @@
         <v>30</v>
       </c>
       <c r="C240" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D240" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E240" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F240" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G240" s="7" t="n">
         <v>0</v>
@@ -39795,16 +39795,16 @@
         <v>30</v>
       </c>
       <c r="C241" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D241" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E241" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F241" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G241" s="7" t="n">
         <v>0</v>
@@ -39818,16 +39818,16 @@
         <v>30</v>
       </c>
       <c r="C242" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D242" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E242" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F242" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G242" s="7" t="n">
         <v>0</v>
@@ -39841,16 +39841,16 @@
         <v>30</v>
       </c>
       <c r="C243" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D243" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E243" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F243" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G243" s="7" t="n">
         <v>0</v>
@@ -39864,16 +39864,16 @@
         <v>30</v>
       </c>
       <c r="C244" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D244" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E244" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F244" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G244" s="7" t="n">
         <v>0</v>
@@ -39887,16 +39887,16 @@
         <v>30</v>
       </c>
       <c r="C245" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D245" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E245" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F245" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G245" s="7" t="n">
         <v>0</v>
@@ -39910,16 +39910,16 @@
         <v>31</v>
       </c>
       <c r="C246" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D246" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E246" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F246" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G246" s="7" t="n">
         <v>0</v>
@@ -39933,16 +39933,16 @@
         <v>31</v>
       </c>
       <c r="C247" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D247" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E247" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F247" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G247" s="7" t="n">
         <v>0</v>
@@ -39956,16 +39956,16 @@
         <v>31</v>
       </c>
       <c r="C248" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D248" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E248" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F248" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G248" s="7" t="n">
         <v>0</v>
@@ -39979,16 +39979,16 @@
         <v>31</v>
       </c>
       <c r="C249" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D249" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E249" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F249" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G249" s="7" t="n">
         <v>0</v>
@@ -40002,16 +40002,16 @@
         <v>31</v>
       </c>
       <c r="C250" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D250" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E250" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F250" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G250" s="7" t="n">
         <v>0</v>
@@ -40025,16 +40025,16 @@
         <v>31</v>
       </c>
       <c r="C251" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D251" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E251" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F251" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G251" s="7" t="n">
         <v>0</v>
@@ -40048,16 +40048,16 @@
         <v>32</v>
       </c>
       <c r="C252" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D252" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E252" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F252" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G252" s="7" t="n">
         <v>0</v>
@@ -40071,16 +40071,16 @@
         <v>32</v>
       </c>
       <c r="C253" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D253" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E253" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F253" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G253" s="7" t="n">
         <v>0</v>
@@ -40094,16 +40094,16 @@
         <v>32</v>
       </c>
       <c r="C254" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D254" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E254" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F254" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G254" s="7" t="n">
         <v>0</v>
@@ -40117,16 +40117,16 @@
         <v>32</v>
       </c>
       <c r="C255" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D255" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E255" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F255" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G255" s="7" t="n">
         <v>0</v>
@@ -40140,16 +40140,16 @@
         <v>32</v>
       </c>
       <c r="C256" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D256" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E256" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F256" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G256" s="7" t="n">
         <v>0</v>
@@ -40163,16 +40163,16 @@
         <v>32</v>
       </c>
       <c r="C257" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D257" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E257" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F257" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G257" s="7" t="n">
         <v>0</v>
@@ -40186,16 +40186,16 @@
         <v>32</v>
       </c>
       <c r="C258" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D258" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E258" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F258" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G258" s="7" t="n">
         <v>0</v>
@@ -40209,16 +40209,16 @@
         <v>32</v>
       </c>
       <c r="C259" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D259" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E259" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F259" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G259" s="7" t="n">
         <v>0</v>
@@ -40232,16 +40232,16 @@
         <v>32</v>
       </c>
       <c r="C260" s="7" t="n">
-        <v>0.0568520188961543</v>
+        <v>0.0611764589412475</v>
       </c>
       <c r="D260" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E260" s="7" t="n">
-        <v>0.0429695215157361</v>
+        <v>0.0425868066330077</v>
       </c>
       <c r="F260" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G260" s="7" t="n">
         <v>0</v>
@@ -40255,16 +40255,16 @@
         <v>33</v>
       </c>
       <c r="C261" s="7" t="n">
-        <v>0.0548623419151197</v>
+        <v>0.0591867819602129</v>
       </c>
       <c r="D261" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E261" s="7" t="n">
-        <v>0.0429812057255019</v>
+        <v>0.0425981157743658</v>
       </c>
       <c r="F261" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G261" s="7" t="n">
         <v>0</v>
@@ -40278,16 +40278,16 @@
         <v>33</v>
       </c>
       <c r="C262" s="7" t="n">
-        <v>0.0548623419151197</v>
+        <v>0.0591867819602129</v>
       </c>
       <c r="D262" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E262" s="7" t="n">
-        <v>0.0429812057255019</v>
+        <v>0.0425981157743658</v>
       </c>
       <c r="F262" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G262" s="7" t="n">
         <v>0</v>
@@ -40301,16 +40301,16 @@
         <v>33</v>
       </c>
       <c r="C263" s="7" t="n">
-        <v>0.0548623419151197</v>
+        <v>0.0591867819602129</v>
       </c>
       <c r="D263" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E263" s="7" t="n">
-        <v>0.0429812057255019</v>
+        <v>0.0425981157743658</v>
       </c>
       <c r="F263" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G263" s="7" t="n">
         <v>0</v>
@@ -40324,16 +40324,16 @@
         <v>33</v>
       </c>
       <c r="C264" s="7" t="n">
-        <v>0.0548623419151197</v>
+        <v>0.0591867819602129</v>
       </c>
       <c r="D264" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E264" s="7" t="n">
-        <v>0.0429812057255019</v>
+        <v>0.0425981157743658</v>
       </c>
       <c r="F264" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G264" s="7" t="n">
         <v>0</v>
@@ -40347,16 +40347,16 @@
         <v>33</v>
       </c>
       <c r="C265" s="7" t="n">
-        <v>0.0548623419151197</v>
+        <v>0.0591867819602129</v>
       </c>
       <c r="D265" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E265" s="7" t="n">
-        <v>0.0429812057255019</v>
+        <v>0.0425981157743658</v>
       </c>
       <c r="F265" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G265" s="7" t="n">
         <v>0</v>
@@ -40370,16 +40370,16 @@
         <v>33</v>
       </c>
       <c r="C266" s="7" t="n">
-        <v>0.0548623419151197</v>
+        <v>0.0591867819602129</v>
       </c>
       <c r="D266" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E266" s="7" t="n">
-        <v>0.0429812057255019</v>
+        <v>0.0425981157743658</v>
       </c>
       <c r="F266" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G266" s="7" t="n">
         <v>0</v>
@@ -40393,16 +40393,16 @@
         <v>33</v>
       </c>
       <c r="C267" s="7" t="n">
-        <v>0.0548623419151197</v>
+        <v>0.0591867819602129</v>
       </c>
       <c r="D267" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E267" s="7" t="n">
-        <v>0.0429812057255019</v>
+        <v>0.0425981157743658</v>
       </c>
       <c r="F267" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G267" s="7" t="n">
         <v>0</v>
@@ -40416,16 +40416,16 @@
         <v>34</v>
       </c>
       <c r="C268" s="7" t="n">
-        <v>0.0523158904389418</v>
+        <v>0.056640330484035</v>
       </c>
       <c r="D268" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E268" s="7" t="n">
-        <v>0.0429733893221753</v>
+        <v>0.0425905491416157</v>
       </c>
       <c r="F268" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G268" s="7" t="n">
         <v>0</v>
@@ -40439,16 +40439,16 @@
         <v>34</v>
       </c>
       <c r="C269" s="7" t="n">
-        <v>0.0523158904389418</v>
+        <v>0.056640330484035</v>
       </c>
       <c r="D269" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E269" s="7" t="n">
-        <v>0.0429733893221753</v>
+        <v>0.0425905491416157</v>
       </c>
       <c r="F269" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G269" s="7" t="n">
         <v>0</v>
@@ -40462,16 +40462,16 @@
         <v>34</v>
       </c>
       <c r="C270" s="7" t="n">
-        <v>0.0523158904389418</v>
+        <v>0.056640330484035</v>
       </c>
       <c r="D270" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E270" s="7" t="n">
-        <v>0.0429733893221753</v>
+        <v>0.0425905491416157</v>
       </c>
       <c r="F270" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G270" s="7" t="n">
         <v>0</v>
@@ -40485,16 +40485,16 @@
         <v>34</v>
       </c>
       <c r="C271" s="7" t="n">
-        <v>0.0523158904389418</v>
+        <v>0.056640330484035</v>
       </c>
       <c r="D271" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E271" s="7" t="n">
-        <v>0.0429733893221753</v>
+        <v>0.0425905491416157</v>
       </c>
       <c r="F271" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G271" s="7" t="n">
         <v>0</v>
@@ -40508,16 +40508,16 @@
         <v>34</v>
       </c>
       <c r="C272" s="7" t="n">
-        <v>0.0523158904389418</v>
+        <v>0.056640330484035</v>
       </c>
       <c r="D272" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E272" s="7" t="n">
-        <v>0.0429733893221753</v>
+        <v>0.0425905491416157</v>
       </c>
       <c r="F272" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G272" s="7" t="n">
         <v>0</v>
@@ -40531,16 +40531,16 @@
         <v>34</v>
       </c>
       <c r="C273" s="7" t="n">
-        <v>0.0523158904389418</v>
+        <v>0.056640330484035</v>
       </c>
       <c r="D273" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E273" s="7" t="n">
-        <v>0.0429733893221753</v>
+        <v>0.0425905491416157</v>
       </c>
       <c r="F273" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G273" s="7" t="n">
         <v>0</v>
@@ -40554,16 +40554,16 @@
         <v>34</v>
       </c>
       <c r="C274" s="7" t="n">
-        <v>0.0523158904389418</v>
+        <v>0.056640330484035</v>
       </c>
       <c r="D274" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E274" s="7" t="n">
-        <v>0.0429733893221753</v>
+        <v>0.0425905491416157</v>
       </c>
       <c r="F274" s="7" t="n">
-        <v>0.0315128144787488</v>
+        <v>0.0314658106733201</v>
       </c>
       <c r="G274" s="7" t="n">
         <v>0</v>
@@ -40577,16 +40577,16 @@
         <v>35</v>
       </c>
       <c r="C275" s="7" t="n">
-        <v>0.0533853686121138</v>
+        <v>0.0577098086572069</v>
       </c>
       <c r="D275" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E275" s="7" t="n">
-        <v>0.0423970544135302</v>
+        <v>0.0420142142329706</v>
       </c>
       <c r="F275" s="7" t="n">
-        <v>0.0315068210104375</v>
+        <v>0.0314598172050088</v>
       </c>
       <c r="G275" s="7" t="n">
         <v>0</v>
@@ -40600,16 +40600,16 @@
         <v>35</v>
       </c>
       <c r="C276" s="7" t="n">
-        <v>0.0533853686121138</v>
+        <v>0.0577098086572069</v>
       </c>
       <c r="D276" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E276" s="7" t="n">
-        <v>0.0423970544135302</v>
+        <v>0.0420142142329706</v>
       </c>
       <c r="F276" s="7" t="n">
-        <v>0.0315068210104375</v>
+        <v>0.0314598172050088</v>
       </c>
       <c r="G276" s="7" t="n">
         <v>0</v>
@@ -40623,16 +40623,16 @@
         <v>35</v>
       </c>
       <c r="C277" s="7" t="n">
-        <v>0.0533853686121138</v>
+        <v>0.0577098086572069</v>
       </c>
       <c r="D277" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E277" s="7" t="n">
-        <v>0.0423970544135302</v>
+        <v>0.0420142142329706</v>
       </c>
       <c r="F277" s="7" t="n">
-        <v>0.0315068210104375</v>
+        <v>0.0314598172050088</v>
       </c>
       <c r="G277" s="7" t="n">
         <v>0</v>
@@ -40646,16 +40646,16 @@
         <v>35</v>
       </c>
       <c r="C278" s="7" t="n">
-        <v>0.0533853686121138</v>
+        <v>0.0577098086572069</v>
       </c>
       <c r="D278" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E278" s="7" t="n">
-        <v>0.0423970544135302</v>
+        <v>0.0420142142329706</v>
       </c>
       <c r="F278" s="7" t="n">
-        <v>0.0315068210104375</v>
+        <v>0.0314598172050088</v>
       </c>
       <c r="G278" s="7" t="n">
         <v>0</v>
@@ -40669,16 +40669,16 @@
         <v>35</v>
       </c>
       <c r="C279" s="7" t="n">
-        <v>0.0533853686121138</v>
+        <v>0.0577098086572069</v>
       </c>
       <c r="D279" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E279" s="7" t="n">
-        <v>0.0423970544135302</v>
+        <v>0.0420142142329706</v>
       </c>
       <c r="F279" s="7" t="n">
-        <v>0.0315068210104375</v>
+        <v>0.0314598172050088</v>
       </c>
       <c r="G279" s="7" t="n">
         <v>0</v>
@@ -40692,16 +40692,16 @@
         <v>35</v>
       </c>
       <c r="C280" s="7" t="n">
-        <v>0.0533853686121138</v>
+        <v>0.0577098086572069</v>
       </c>
       <c r="D280" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E280" s="7" t="n">
-        <v>0.0423970544135302</v>
+        <v>0.0420142142329706</v>
       </c>
       <c r="F280" s="7" t="n">
-        <v>0.0315068210104375</v>
+        <v>0.0314598172050088</v>
       </c>
       <c r="G280" s="7" t="n">
         <v>0</v>
@@ -40715,16 +40715,16 @@
         <v>35</v>
       </c>
       <c r="C281" s="7" t="n">
-        <v>0.0533853686121138</v>
+        <v>0.0577098086572069</v>
       </c>
       <c r="D281" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E281" s="7" t="n">
-        <v>0.0423970544135302</v>
+        <v>0.0420142142329706</v>
       </c>
       <c r="F281" s="7" t="n">
-        <v>0.0315068210104375</v>
+        <v>0.0314598172050088</v>
       </c>
       <c r="G281" s="7" t="n">
         <v>0</v>
@@ -40738,16 +40738,16 @@
         <v>35</v>
       </c>
       <c r="C282" s="7" t="n">
-        <v>0.0533853686121138</v>
+        <v>0.0577098086572069</v>
       </c>
       <c r="D282" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E282" s="7" t="n">
-        <v>0.0423970544135302</v>
+        <v>0.0420142142329706</v>
       </c>
       <c r="F282" s="7" t="n">
-        <v>0.0315068210104375</v>
+        <v>0.0314598172050088</v>
       </c>
       <c r="G282" s="7" t="n">
         <v>0</v>
@@ -40761,16 +40761,16 @@
         <v>35</v>
       </c>
       <c r="C283" s="7" t="n">
-        <v>0.0533853686121138</v>
+        <v>0.0577098086572069</v>
       </c>
       <c r="D283" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E283" s="7" t="n">
-        <v>0.0423970544135302</v>
+        <v>0.0420142142329706</v>
       </c>
       <c r="F283" s="7" t="n">
-        <v>0.0315068210104375</v>
+        <v>0.0314598172050088</v>
       </c>
       <c r="G283" s="7" t="n">
         <v>0</v>
@@ -40784,16 +40784,16 @@
         <v>35</v>
       </c>
       <c r="C284" s="7" t="n">
-        <v>0.0533853686121138</v>
+        <v>0.0577098086572069</v>
       </c>
       <c r="D284" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E284" s="7" t="n">
-        <v>0.0423970544135302</v>
+        <v>0.0420142142329706</v>
       </c>
       <c r="F284" s="7" t="n">
-        <v>0.0315068210104375</v>
+        <v>0.0314598172050088</v>
       </c>
       <c r="G284" s="7" t="n">
         <v>0</v>
@@ -40807,16 +40807,16 @@
         <v>36</v>
       </c>
       <c r="C285" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D285" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E285" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F285" s="7" t="n">
-        <v>0.0314743720316276</v>
+        <v>0.0314274049546782</v>
       </c>
       <c r="G285" s="7" t="n">
         <v>0</v>
@@ -40830,16 +40830,16 @@
         <v>36</v>
       </c>
       <c r="C286" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D286" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E286" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F286" s="7" t="n">
-        <v>0.0314743720316276</v>
+        <v>0.0314274049546782</v>
       </c>
       <c r="G286" s="7" t="n">
         <v>0</v>
@@ -40853,16 +40853,16 @@
         <v>36</v>
       </c>
       <c r="C287" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D287" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E287" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F287" s="7" t="n">
-        <v>0.0314743720316276</v>
+        <v>0.0314274049546782</v>
       </c>
       <c r="G287" s="7" t="n">
         <v>0</v>
@@ -40876,16 +40876,16 @@
         <v>36</v>
       </c>
       <c r="C288" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D288" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E288" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F288" s="7" t="n">
-        <v>0.0314743720316276</v>
+        <v>0.0314274049546782</v>
       </c>
       <c r="G288" s="7" t="n">
         <v>0</v>
@@ -40899,16 +40899,16 @@
         <v>36</v>
       </c>
       <c r="C289" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D289" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E289" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F289" s="7" t="n">
-        <v>0.0314743720316276</v>
+        <v>0.0314274049546782</v>
       </c>
       <c r="G289" s="7" t="n">
         <v>0</v>
@@ -40922,16 +40922,16 @@
         <v>36</v>
       </c>
       <c r="C290" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D290" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E290" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F290" s="7" t="n">
-        <v>0.0314743720316276</v>
+        <v>0.0314274049546782</v>
       </c>
       <c r="G290" s="7" t="n">
         <v>0</v>
@@ -40945,16 +40945,16 @@
         <v>36</v>
       </c>
       <c r="C291" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D291" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E291" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F291" s="7" t="n">
-        <v>0.0314743720316276</v>
+        <v>0.0314274049546782</v>
       </c>
       <c r="G291" s="7" t="n">
         <v>0</v>
@@ -40968,16 +40968,16 @@
         <v>36</v>
       </c>
       <c r="C292" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D292" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E292" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F292" s="7" t="n">
-        <v>0.0314743720316276</v>
+        <v>0.0314274049546782</v>
       </c>
       <c r="G292" s="7" t="n">
         <v>0</v>
@@ -40991,16 +40991,16 @@
         <v>36</v>
       </c>
       <c r="C293" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D293" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E293" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F293" s="7" t="n">
-        <v>0.0314743720316276</v>
+        <v>0.0314274049546782</v>
       </c>
       <c r="G293" s="7" t="n">
         <v>0</v>
@@ -41014,16 +41014,16 @@
         <v>37</v>
       </c>
       <c r="C294" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D294" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E294" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F294" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G294" s="7" t="n">
         <v>0</v>
@@ -41037,16 +41037,16 @@
         <v>37</v>
       </c>
       <c r="C295" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D295" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E295" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F295" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G295" s="7" t="n">
         <v>0</v>
@@ -41060,16 +41060,16 @@
         <v>37</v>
       </c>
       <c r="C296" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D296" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E296" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F296" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G296" s="7" t="n">
         <v>0</v>
@@ -41083,16 +41083,16 @@
         <v>37</v>
       </c>
       <c r="C297" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D297" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E297" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F297" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G297" s="7" t="n">
         <v>0</v>
@@ -41106,16 +41106,16 @@
         <v>37</v>
       </c>
       <c r="C298" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D298" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E298" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F298" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G298" s="7" t="n">
         <v>0</v>
@@ -41129,16 +41129,16 @@
         <v>37</v>
       </c>
       <c r="C299" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D299" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E299" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F299" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G299" s="7" t="n">
         <v>0</v>
@@ -41152,16 +41152,16 @@
         <v>37</v>
       </c>
       <c r="C300" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D300" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E300" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F300" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G300" s="7" t="n">
         <v>0</v>
@@ -41175,16 +41175,16 @@
         <v>38</v>
       </c>
       <c r="C301" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D301" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E301" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F301" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G301" s="7" t="n">
         <v>0</v>
@@ -41198,16 +41198,16 @@
         <v>38</v>
       </c>
       <c r="C302" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D302" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E302" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F302" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G302" s="7" t="n">
         <v>0</v>
@@ -41221,16 +41221,16 @@
         <v>38</v>
       </c>
       <c r="C303" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D303" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E303" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F303" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G303" s="7" t="n">
         <v>0</v>
@@ -41244,16 +41244,16 @@
         <v>38</v>
       </c>
       <c r="C304" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D304" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E304" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F304" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G304" s="7" t="n">
         <v>0</v>
@@ -41267,16 +41267,16 @@
         <v>38</v>
       </c>
       <c r="C305" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D305" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E305" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F305" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G305" s="7" t="n">
         <v>0</v>
@@ -41290,16 +41290,16 @@
         <v>38</v>
       </c>
       <c r="C306" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D306" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E306" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F306" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G306" s="7" t="n">
         <v>0</v>
@@ -41313,16 +41313,16 @@
         <v>38</v>
       </c>
       <c r="C307" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D307" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E307" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F307" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G307" s="7" t="n">
         <v>0</v>
@@ -41336,16 +41336,16 @@
         <v>38</v>
       </c>
       <c r="C308" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D308" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E308" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F308" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G308" s="7" t="n">
         <v>0</v>
@@ -41359,16 +41359,16 @@
         <v>38</v>
       </c>
       <c r="C309" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D309" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E309" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F309" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G309" s="7" t="n">
         <v>0</v>
@@ -41382,16 +41382,16 @@
         <v>39</v>
       </c>
       <c r="C310" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D310" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E310" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F310" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G310" s="7" t="n">
         <v>0</v>
@@ -41405,16 +41405,16 @@
         <v>39</v>
       </c>
       <c r="C311" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D311" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E311" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F311" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G311" s="7" t="n">
         <v>0</v>
@@ -41428,16 +41428,16 @@
         <v>39</v>
       </c>
       <c r="C312" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D312" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E312" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F312" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G312" s="7" t="n">
         <v>0</v>
@@ -41451,16 +41451,16 @@
         <v>39</v>
       </c>
       <c r="C313" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D313" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E313" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F313" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G313" s="7" t="n">
         <v>0</v>
@@ -41474,16 +41474,16 @@
         <v>39</v>
       </c>
       <c r="C314" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D314" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E314" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F314" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G314" s="7" t="n">
         <v>0</v>
@@ -41497,16 +41497,16 @@
         <v>40</v>
       </c>
       <c r="C315" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D315" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E315" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F315" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G315" s="7" t="n">
         <v>0</v>
@@ -41520,16 +41520,16 @@
         <v>40</v>
       </c>
       <c r="C316" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D316" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E316" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F316" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G316" s="7" t="n">
         <v>0</v>
@@ -41543,16 +41543,16 @@
         <v>40</v>
       </c>
       <c r="C317" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D317" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E317" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F317" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G317" s="7" t="n">
         <v>0</v>
@@ -41566,16 +41566,16 @@
         <v>40</v>
       </c>
       <c r="C318" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D318" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E318" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F318" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G318" s="7" t="n">
         <v>0</v>
@@ -41589,16 +41589,16 @@
         <v>40</v>
       </c>
       <c r="C319" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D319" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E319" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F319" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G319" s="7" t="n">
         <v>0</v>
@@ -41612,16 +41612,16 @@
         <v>40</v>
       </c>
       <c r="C320" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D320" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E320" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F320" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G320" s="7" t="n">
         <v>0</v>
@@ -41635,16 +41635,16 @@
         <v>40</v>
       </c>
       <c r="C321" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D321" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E321" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F321" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G321" s="7" t="n">
         <v>0</v>
@@ -41658,16 +41658,16 @@
         <v>41</v>
       </c>
       <c r="C322" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D322" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E322" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F322" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G322" s="7" t="n">
         <v>0</v>
@@ -41681,16 +41681,16 @@
         <v>41</v>
       </c>
       <c r="C323" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D323" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E323" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F323" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G323" s="7" t="n">
         <v>0</v>
@@ -41704,16 +41704,16 @@
         <v>41</v>
       </c>
       <c r="C324" s="7" t="n">
-        <v>0.0547890335451625</v>
+        <v>0.0592708698470636</v>
       </c>
       <c r="D324" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E324" s="7" t="n">
-        <v>0.0421343687219288</v>
+        <v>0.0417523235980074</v>
       </c>
       <c r="F324" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G324" s="7" t="n">
         <v>0</v>
@@ -41727,16 +41727,16 @@
         <v>42</v>
       </c>
       <c r="C325" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D325" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E325" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F325" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G325" s="7" t="n">
         <v>0</v>
@@ -41750,16 +41750,16 @@
         <v>42</v>
       </c>
       <c r="C326" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D326" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E326" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F326" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G326" s="7" t="n">
         <v>0</v>
@@ -41773,16 +41773,16 @@
         <v>42</v>
       </c>
       <c r="C327" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D327" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E327" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F327" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G327" s="7" t="n">
         <v>0</v>
@@ -41796,16 +41796,16 @@
         <v>42</v>
       </c>
       <c r="C328" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D328" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E328" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F328" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G328" s="7" t="n">
         <v>0</v>
@@ -41819,16 +41819,16 @@
         <v>42</v>
       </c>
       <c r="C329" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D329" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E329" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F329" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G329" s="7" t="n">
         <v>0</v>
@@ -41842,16 +41842,16 @@
         <v>42</v>
       </c>
       <c r="C330" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D330" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E330" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F330" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G330" s="7" t="n">
         <v>0</v>
@@ -41865,16 +41865,16 @@
         <v>42</v>
       </c>
       <c r="C331" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D331" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E331" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F331" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G331" s="7" t="n">
         <v>0</v>
@@ -41888,16 +41888,16 @@
         <v>42</v>
       </c>
       <c r="C332" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D332" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E332" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F332" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G332" s="7" t="n">
         <v>0</v>
@@ -41911,16 +41911,16 @@
         <v>42</v>
       </c>
       <c r="C333" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D333" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E333" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F333" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G333" s="7" t="n">
         <v>0</v>
@@ -41934,16 +41934,16 @@
         <v>42</v>
       </c>
       <c r="C334" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D334" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E334" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F334" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G334" s="7" t="n">
         <v>0</v>
@@ -41957,16 +41957,16 @@
         <v>42</v>
       </c>
       <c r="C335" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D335" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E335" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F335" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G335" s="7" t="n">
         <v>0</v>
@@ -41980,16 +41980,16 @@
         <v>42</v>
       </c>
       <c r="C336" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D336" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E336" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F336" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G336" s="7" t="n">
         <v>0</v>
@@ -42003,16 +42003,16 @@
         <v>42</v>
       </c>
       <c r="C337" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D337" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E337" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F337" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G337" s="7" t="n">
         <v>0</v>
@@ -42026,16 +42026,16 @@
         <v>42</v>
       </c>
       <c r="C338" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D338" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E338" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F338" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G338" s="7" t="n">
         <v>0</v>
@@ -42049,16 +42049,16 @@
         <v>42</v>
       </c>
       <c r="C339" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D339" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E339" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F339" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G339" s="7" t="n">
         <v>0</v>
@@ -42072,16 +42072,16 @@
         <v>42</v>
       </c>
       <c r="C340" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D340" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E340" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F340" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G340" s="7" t="n">
         <v>0</v>
@@ -42095,16 +42095,16 @@
         <v>42</v>
       </c>
       <c r="C341" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D341" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E341" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F341" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G341" s="7" t="n">
         <v>0</v>
@@ -42118,16 +42118,16 @@
         <v>42</v>
       </c>
       <c r="C342" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D342" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E342" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F342" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G342" s="7" t="n">
         <v>0</v>
@@ -42141,16 +42141,16 @@
         <v>42</v>
       </c>
       <c r="C343" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D343" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E343" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F343" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G343" s="7" t="n">
         <v>0</v>
@@ -42164,16 +42164,16 @@
         <v>42</v>
       </c>
       <c r="C344" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D344" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E344" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F344" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G344" s="7" t="n">
         <v>0</v>
@@ -42187,16 +42187,16 @@
         <v>42</v>
       </c>
       <c r="C345" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D345" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E345" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F345" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G345" s="7" t="n">
         <v>0</v>
@@ -42210,16 +42210,16 @@
         <v>42</v>
       </c>
       <c r="C346" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D346" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E346" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F346" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G346" s="7" t="n">
         <v>0</v>
@@ -42233,16 +42233,16 @@
         <v>42</v>
       </c>
       <c r="C347" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D347" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E347" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F347" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G347" s="7" t="n">
         <v>0</v>
@@ -42256,16 +42256,16 @@
         <v>42</v>
       </c>
       <c r="C348" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D348" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E348" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F348" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G348" s="7" t="n">
         <v>0</v>
@@ -42279,16 +42279,16 @@
         <v>42</v>
       </c>
       <c r="C349" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D349" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E349" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F349" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G349" s="7" t="n">
         <v>0</v>
@@ -42302,16 +42302,16 @@
         <v>42</v>
       </c>
       <c r="C350" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D350" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E350" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F350" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G350" s="7" t="n">
         <v>0</v>
@@ -42325,16 +42325,16 @@
         <v>42</v>
       </c>
       <c r="C351" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D351" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E351" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F351" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G351" s="7" t="n">
         <v>0</v>
@@ -42348,16 +42348,16 @@
         <v>42</v>
       </c>
       <c r="C352" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D352" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E352" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F352" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G352" s="7" t="n">
         <v>0</v>
@@ -42371,16 +42371,16 @@
         <v>42</v>
       </c>
       <c r="C353" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D353" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E353" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F353" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G353" s="7" t="n">
         <v>0</v>
@@ -42394,16 +42394,16 @@
         <v>42</v>
       </c>
       <c r="C354" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D354" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E354" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F354" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G354" s="7" t="n">
         <v>0</v>
@@ -42417,16 +42417,16 @@
         <v>42</v>
       </c>
       <c r="C355" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D355" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E355" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F355" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G355" s="7" t="n">
         <v>0</v>
@@ -42440,16 +42440,16 @@
         <v>42</v>
       </c>
       <c r="C356" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D356" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E356" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F356" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G356" s="7" t="n">
         <v>0</v>
@@ -42463,16 +42463,16 @@
         <v>42</v>
       </c>
       <c r="C357" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D357" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E357" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F357" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G357" s="7" t="n">
         <v>0</v>
@@ -42486,16 +42486,16 @@
         <v>42</v>
       </c>
       <c r="C358" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D358" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E358" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F358" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G358" s="7" t="n">
         <v>0</v>
@@ -42509,16 +42509,16 @@
         <v>42</v>
       </c>
       <c r="C359" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D359" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E359" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F359" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G359" s="7" t="n">
         <v>0</v>
@@ -42532,16 +42532,16 @@
         <v>42</v>
       </c>
       <c r="C360" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D360" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E360" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F360" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G360" s="7" t="n">
         <v>0</v>
@@ -42555,16 +42555,16 @@
         <v>42</v>
       </c>
       <c r="C361" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D361" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E361" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F361" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G361" s="7" t="n">
         <v>0</v>
@@ -42578,16 +42578,16 @@
         <v>42</v>
       </c>
       <c r="C362" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D362" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E362" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F362" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G362" s="7" t="n">
         <v>0</v>
@@ -42601,16 +42601,16 @@
         <v>42</v>
       </c>
       <c r="C363" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D363" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E363" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F363" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G363" s="7" t="n">
         <v>0</v>
@@ -42624,16 +42624,16 @@
         <v>42</v>
       </c>
       <c r="C364" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D364" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E364" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F364" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G364" s="7" t="n">
         <v>0</v>
@@ -42647,16 +42647,16 @@
         <v>42</v>
       </c>
       <c r="C365" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D365" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E365" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F365" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G365" s="7" t="n">
         <v>0</v>
@@ -42670,16 +42670,16 @@
         <v>42</v>
       </c>
       <c r="C366" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D366" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E366" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F366" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G366" s="7" t="n">
         <v>0</v>
@@ -42693,16 +42693,16 @@
         <v>42</v>
       </c>
       <c r="C367" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D367" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E367" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F367" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G367" s="7" t="n">
         <v>0</v>
@@ -42716,16 +42716,16 @@
         <v>42</v>
       </c>
       <c r="C368" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D368" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E368" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F368" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G368" s="7" t="n">
         <v>0</v>
@@ -42739,16 +42739,16 @@
         <v>42</v>
       </c>
       <c r="C369" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D369" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E369" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F369" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G369" s="7" t="n">
         <v>0</v>
@@ -42762,16 +42762,16 @@
         <v>42</v>
       </c>
       <c r="C370" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D370" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E370" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F370" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G370" s="7" t="n">
         <v>0</v>
@@ -42785,16 +42785,16 @@
         <v>42</v>
       </c>
       <c r="C371" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D371" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E371" s="7" t="n">
-        <v>0.0412635700565624</v>
+        <v>0.0408847352120823</v>
       </c>
       <c r="F371" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G371" s="7" t="n">
         <v>0</v>
@@ -42808,16 +42808,16 @@
         <v>43</v>
       </c>
       <c r="C372" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D372" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E372" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F372" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G372" s="7" t="n">
         <v>0</v>
@@ -42831,16 +42831,16 @@
         <v>43</v>
       </c>
       <c r="C373" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D373" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E373" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F373" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G373" s="7" t="n">
         <v>0</v>
@@ -42854,16 +42854,16 @@
         <v>43</v>
       </c>
       <c r="C374" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D374" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E374" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F374" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G374" s="7" t="n">
         <v>0</v>
@@ -42877,16 +42877,16 @@
         <v>43</v>
       </c>
       <c r="C375" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D375" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E375" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F375" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G375" s="7" t="n">
         <v>0</v>
@@ -42900,16 +42900,16 @@
         <v>43</v>
       </c>
       <c r="C376" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D376" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E376" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F376" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G376" s="7" t="n">
         <v>0</v>
@@ -42923,16 +42923,16 @@
         <v>43</v>
       </c>
       <c r="C377" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D377" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E377" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F377" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G377" s="7" t="n">
         <v>0</v>
@@ -42946,16 +42946,16 @@
         <v>43</v>
       </c>
       <c r="C378" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D378" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E378" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F378" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G378" s="7" t="n">
         <v>0</v>
@@ -42969,16 +42969,16 @@
         <v>43</v>
       </c>
       <c r="C379" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D379" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E379" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F379" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G379" s="7" t="n">
         <v>0</v>
@@ -42992,16 +42992,16 @@
         <v>43</v>
       </c>
       <c r="C380" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D380" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E380" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F380" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G380" s="7" t="n">
         <v>0</v>
@@ -43015,16 +43015,16 @@
         <v>43</v>
       </c>
       <c r="C381" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D381" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E381" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F381" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G381" s="7" t="n">
         <v>0</v>
@@ -43038,16 +43038,16 @@
         <v>43</v>
       </c>
       <c r="C382" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D382" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E382" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F382" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G382" s="7" t="n">
         <v>0</v>
@@ -43061,16 +43061,16 @@
         <v>43</v>
       </c>
       <c r="C383" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D383" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E383" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F383" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G383" s="7" t="n">
         <v>0</v>
@@ -43084,16 +43084,16 @@
         <v>43</v>
       </c>
       <c r="C384" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D384" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E384" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F384" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G384" s="7" t="n">
         <v>0</v>
@@ -43107,16 +43107,16 @@
         <v>43</v>
       </c>
       <c r="C385" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D385" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E385" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F385" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G385" s="7" t="n">
         <v>0</v>
@@ -43130,16 +43130,16 @@
         <v>43</v>
       </c>
       <c r="C386" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D386" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E386" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F386" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G386" s="7" t="n">
         <v>0</v>
@@ -43153,16 +43153,16 @@
         <v>44</v>
       </c>
       <c r="C387" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D387" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E387" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F387" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G387" s="7" t="n">
         <v>0</v>
@@ -43176,16 +43176,16 @@
         <v>44</v>
       </c>
       <c r="C388" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D388" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E388" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F388" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G388" s="7" t="n">
         <v>0</v>
@@ -43199,16 +43199,16 @@
         <v>44</v>
       </c>
       <c r="C389" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D389" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E389" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F389" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G389" s="7" t="n">
         <v>0</v>
@@ -43222,16 +43222,16 @@
         <v>44</v>
       </c>
       <c r="C390" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D390" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E390" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F390" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G390" s="7" t="n">
         <v>0</v>
@@ -43245,16 +43245,16 @@
         <v>44</v>
       </c>
       <c r="C391" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D391" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E391" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F391" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G391" s="7" t="n">
         <v>0</v>
@@ -43268,16 +43268,16 @@
         <v>44</v>
       </c>
       <c r="C392" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D392" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E392" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F392" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G392" s="7" t="n">
         <v>0</v>
@@ -43291,16 +43291,16 @@
         <v>44</v>
       </c>
       <c r="C393" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D393" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E393" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F393" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G393" s="7" t="n">
         <v>0</v>
@@ -43314,16 +43314,16 @@
         <v>44</v>
       </c>
       <c r="C394" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D394" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E394" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F394" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G394" s="7" t="n">
         <v>0</v>
@@ -43337,16 +43337,16 @@
         <v>44</v>
       </c>
       <c r="C395" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D395" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E395" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F395" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G395" s="7" t="n">
         <v>0</v>
@@ -43360,16 +43360,16 @@
         <v>44</v>
       </c>
       <c r="C396" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D396" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E396" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F396" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G396" s="7" t="n">
         <v>0</v>
@@ -43383,16 +43383,16 @@
         <v>44</v>
       </c>
       <c r="C397" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D397" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E397" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F397" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G397" s="7" t="n">
         <v>0</v>
@@ -43406,16 +43406,16 @@
         <v>44</v>
       </c>
       <c r="C398" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D398" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E398" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F398" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G398" s="7" t="n">
         <v>0</v>
@@ -43429,16 +43429,16 @@
         <v>44</v>
       </c>
       <c r="C399" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D399" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E399" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F399" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G399" s="7" t="n">
         <v>0</v>
@@ -43452,16 +43452,16 @@
         <v>44</v>
       </c>
       <c r="C400" s="7" t="n">
-        <v>0.0530598965558432</v>
+        <v>0.0575417328577443</v>
       </c>
       <c r="D400" s="7" t="n">
         <v>0.0151015125519547</v>
       </c>
       <c r="E400" s="7" t="n">
-        <v>0.0412624408718974</v>
+        <v>0.0408836426147748</v>
       </c>
       <c r="F400" s="7" t="n">
-        <v>0.0181689551848949</v>
+        <v>0.0181220456083792</v>
       </c>
       <c r="G400" s="7" t="n">
         <v>0</v>
@@ -43475,16 +43475,16 @@
         <v>45</v>
       </c>
       <c r="C401" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D401" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E401" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F401" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G401" s="7" t="n">
         <v>0</v>
@@ -43498,16 +43498,16 @@
         <v>45</v>
       </c>
       <c r="C402" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D402" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E402" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F402" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G402" s="7" t="n">
         <v>0</v>
@@ -43521,16 +43521,16 @@
         <v>45</v>
       </c>
       <c r="C403" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D403" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E403" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F403" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G403" s="7" t="n">
         <v>0</v>
@@ -43544,16 +43544,16 @@
         <v>45</v>
       </c>
       <c r="C404" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D404" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E404" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F404" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G404" s="7" t="n">
         <v>0</v>
@@ -43567,16 +43567,16 @@
         <v>45</v>
       </c>
       <c r="C405" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D405" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E405" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F405" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G405" s="7" t="n">
         <v>0</v>
@@ -43590,16 +43590,16 @@
         <v>45</v>
       </c>
       <c r="C406" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D406" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E406" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F406" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G406" s="7" t="n">
         <v>0</v>
@@ -43613,16 +43613,16 @@
         <v>45</v>
       </c>
       <c r="C407" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D407" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E407" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F407" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G407" s="7" t="n">
         <v>0</v>
@@ -43636,16 +43636,16 @@
         <v>45</v>
       </c>
       <c r="C408" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D408" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E408" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F408" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G408" s="7" t="n">
         <v>0</v>
@@ -43659,16 +43659,16 @@
         <v>45</v>
       </c>
       <c r="C409" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D409" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E409" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F409" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G409" s="7" t="n">
         <v>0</v>
@@ -43682,16 +43682,16 @@
         <v>45</v>
       </c>
       <c r="C410" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D410" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E410" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F410" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G410" s="7" t="n">
         <v>0</v>
@@ -43705,16 +43705,16 @@
         <v>45</v>
       </c>
       <c r="C411" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D411" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E411" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F411" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G411" s="7" t="n">
         <v>0</v>
@@ -43728,16 +43728,16 @@
         <v>45</v>
       </c>
       <c r="C412" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D412" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E412" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F412" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G412" s="7" t="n">
         <v>0</v>
@@ -43751,16 +43751,16 @@
         <v>45</v>
       </c>
       <c r="C413" s="7" t="n">
-        <v>0.0515682430659276</v>
+        <v>0.0560093460445773</v>
       </c>
       <c r="D413" s="7" t="n">
         <v>0.0139193832158971</v>
       </c>
       <c r="E413" s="7" t="n">
-        <v>0.0410026387676907</v>
+        <v>0.0406238405105681</v>
       </c>
       <c r="F413" s="7" t="n">
-        <v>0.0174679979251785</v>
+        <v>0.0174211363716391</v>
       </c>
       <c r="G413" s="7" t="n">
         <v>0</v>
@@ -43774,16 +43774,16 @@
         <v>46</v>
       </c>
       <c r="C414" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D414" s="7" t="n">
         <v>0.0139193833879646</v>
       </c>
       <c r="E414" s="7" t="n">
-        <v>0.0384112878491988</v>
+        <v>0.0380565472832017</v>
       </c>
       <c r="F414" s="7" t="n">
-        <v>0.0174679979940055</v>
+        <v>0.0174211364404661</v>
       </c>
       <c r="G414" s="7" t="n">
         <v>0</v>
@@ -43797,16 +43797,16 @@
         <v>46</v>
       </c>
       <c r="C415" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D415" s="7" t="n">
         <v>0.0139193833879646</v>
       </c>
       <c r="E415" s="7" t="n">
-        <v>0.0384112878491988</v>
+        <v>0.0380565472832017</v>
       </c>
       <c r="F415" s="7" t="n">
-        <v>0.0174679979940055</v>
+        <v>0.0174211364404661</v>
       </c>
       <c r="G415" s="7" t="n">
         <v>0</v>
@@ -43820,16 +43820,16 @@
         <v>46</v>
       </c>
       <c r="C416" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D416" s="7" t="n">
         <v>0.0139193833879646</v>
       </c>
       <c r="E416" s="7" t="n">
-        <v>0.0384112878491988</v>
+        <v>0.0380565472832017</v>
       </c>
       <c r="F416" s="7" t="n">
-        <v>0.0174679979940055</v>
+        <v>0.0174211364404661</v>
       </c>
       <c r="G416" s="7" t="n">
         <v>0</v>
@@ -43843,16 +43843,16 @@
         <v>46</v>
       </c>
       <c r="C417" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D417" s="7" t="n">
         <v>0.0139193833879646</v>
       </c>
       <c r="E417" s="7" t="n">
-        <v>0.0384112878491988</v>
+        <v>0.0380565472832017</v>
       </c>
       <c r="F417" s="7" t="n">
-        <v>0.0174679979940055</v>
+        <v>0.0174211364404661</v>
       </c>
       <c r="G417" s="7" t="n">
         <v>0</v>
@@ -43866,16 +43866,16 @@
         <v>46</v>
       </c>
       <c r="C418" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D418" s="7" t="n">
         <v>0.0139193833879646</v>
       </c>
       <c r="E418" s="7" t="n">
-        <v>0.0384112878491988</v>
+        <v>0.0380565472832017</v>
       </c>
       <c r="F418" s="7" t="n">
-        <v>0.0174679979940055</v>
+        <v>0.0174211364404661</v>
       </c>
       <c r="G418" s="7" t="n">
         <v>0</v>
@@ -43889,16 +43889,16 @@
         <v>46</v>
       </c>
       <c r="C419" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D419" s="7" t="n">
         <v>0.0139193833879646</v>
       </c>
       <c r="E419" s="7" t="n">
-        <v>0.0384112878491988</v>
+        <v>0.0380565472832017</v>
       </c>
       <c r="F419" s="7" t="n">
-        <v>0.0174679979940055</v>
+        <v>0.0174211364404661</v>
       </c>
       <c r="G419" s="7" t="n">
         <v>0</v>
@@ -43912,16 +43912,16 @@
         <v>46</v>
       </c>
       <c r="C420" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D420" s="7" t="n">
         <v>0.0139193833879646</v>
       </c>
       <c r="E420" s="7" t="n">
-        <v>0.0384112878491988</v>
+        <v>0.0380565472832017</v>
       </c>
       <c r="F420" s="7" t="n">
-        <v>0.0174679979940055</v>
+        <v>0.0174211364404661</v>
       </c>
       <c r="G420" s="7" t="n">
         <v>0</v>
@@ -43935,16 +43935,16 @@
         <v>46</v>
       </c>
       <c r="C421" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D421" s="7" t="n">
         <v>0.0139193833879646</v>
       </c>
       <c r="E421" s="7" t="n">
-        <v>0.0384112878491988</v>
+        <v>0.0380565472832017</v>
       </c>
       <c r="F421" s="7" t="n">
-        <v>0.0174679979940055</v>
+        <v>0.0174211364404661</v>
       </c>
       <c r="G421" s="7" t="n">
         <v>0</v>
@@ -43958,7 +43958,7 @@
         <v>47</v>
       </c>
       <c r="C422" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D422" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -43970,7 +43970,7 @@
         <v>0</v>
       </c>
       <c r="G422" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="423">
@@ -43981,7 +43981,7 @@
         <v>47</v>
       </c>
       <c r="C423" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D423" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -43993,7 +43993,7 @@
         <v>0</v>
       </c>
       <c r="G423" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="424">
@@ -44004,7 +44004,7 @@
         <v>47</v>
       </c>
       <c r="C424" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D424" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44016,7 +44016,7 @@
         <v>0</v>
       </c>
       <c r="G424" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="425">
@@ -44027,7 +44027,7 @@
         <v>47</v>
       </c>
       <c r="C425" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D425" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44039,7 +44039,7 @@
         <v>0</v>
       </c>
       <c r="G425" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="426">
@@ -44050,7 +44050,7 @@
         <v>47</v>
       </c>
       <c r="C426" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D426" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44062,7 +44062,7 @@
         <v>0</v>
       </c>
       <c r="G426" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="427">
@@ -44073,7 +44073,7 @@
         <v>47</v>
       </c>
       <c r="C427" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D427" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44085,7 +44085,7 @@
         <v>0</v>
       </c>
       <c r="G427" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="428">
@@ -44096,7 +44096,7 @@
         <v>47</v>
       </c>
       <c r="C428" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D428" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44108,7 +44108,7 @@
         <v>0</v>
       </c>
       <c r="G428" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="429">
@@ -44119,7 +44119,7 @@
         <v>47</v>
       </c>
       <c r="C429" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D429" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44131,7 +44131,7 @@
         <v>0</v>
       </c>
       <c r="G429" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="430">
@@ -44142,7 +44142,7 @@
         <v>47</v>
       </c>
       <c r="C430" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D430" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44154,7 +44154,7 @@
         <v>0</v>
       </c>
       <c r="G430" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="431">
@@ -44165,7 +44165,7 @@
         <v>47</v>
       </c>
       <c r="C431" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D431" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44177,7 +44177,7 @@
         <v>0</v>
       </c>
       <c r="G431" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="432">
@@ -44188,7 +44188,7 @@
         <v>47</v>
       </c>
       <c r="C432" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D432" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44200,7 +44200,7 @@
         <v>0</v>
       </c>
       <c r="G432" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="433">
@@ -44211,7 +44211,7 @@
         <v>47</v>
       </c>
       <c r="C433" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D433" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44223,7 +44223,7 @@
         <v>0</v>
       </c>
       <c r="G433" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="434">
@@ -44234,7 +44234,7 @@
         <v>47</v>
       </c>
       <c r="C434" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D434" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44246,7 +44246,7 @@
         <v>0</v>
       </c>
       <c r="G434" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="435">
@@ -44257,7 +44257,7 @@
         <v>47</v>
       </c>
       <c r="C435" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D435" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44269,7 +44269,7 @@
         <v>0</v>
       </c>
       <c r="G435" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="436">
@@ -44280,7 +44280,7 @@
         <v>47</v>
       </c>
       <c r="C436" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D436" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44292,7 +44292,7 @@
         <v>0</v>
       </c>
       <c r="G436" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="437">
@@ -44303,7 +44303,7 @@
         <v>47</v>
       </c>
       <c r="C437" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D437" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44315,7 +44315,7 @@
         <v>0</v>
       </c>
       <c r="G437" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="438">
@@ -44326,7 +44326,7 @@
         <v>47</v>
       </c>
       <c r="C438" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D438" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44338,7 +44338,7 @@
         <v>0</v>
       </c>
       <c r="G438" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="439">
@@ -44349,7 +44349,7 @@
         <v>47</v>
       </c>
       <c r="C439" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D439" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44361,7 +44361,7 @@
         <v>0</v>
       </c>
       <c r="G439" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="440">
@@ -44372,7 +44372,7 @@
         <v>47</v>
       </c>
       <c r="C440" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D440" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44384,7 +44384,7 @@
         <v>0</v>
       </c>
       <c r="G440" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="441">
@@ -44395,7 +44395,7 @@
         <v>47</v>
       </c>
       <c r="C441" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D441" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44407,7 +44407,7 @@
         <v>0</v>
       </c>
       <c r="G441" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="442">
@@ -44418,7 +44418,7 @@
         <v>47</v>
       </c>
       <c r="C442" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D442" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44430,7 +44430,7 @@
         <v>0</v>
       </c>
       <c r="G442" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="443">
@@ -44441,7 +44441,7 @@
         <v>47</v>
       </c>
       <c r="C443" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D443" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44453,7 +44453,7 @@
         <v>0</v>
       </c>
       <c r="G443" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="444">
@@ -44464,7 +44464,7 @@
         <v>47</v>
       </c>
       <c r="C444" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D444" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44476,7 +44476,7 @@
         <v>0</v>
       </c>
       <c r="G444" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="445">
@@ -44487,7 +44487,7 @@
         <v>47</v>
       </c>
       <c r="C445" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D445" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44499,7 +44499,7 @@
         <v>0</v>
       </c>
       <c r="G445" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="446">
@@ -44510,7 +44510,7 @@
         <v>47</v>
       </c>
       <c r="C446" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D446" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44522,7 +44522,7 @@
         <v>0</v>
       </c>
       <c r="G446" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="447">
@@ -44533,7 +44533,7 @@
         <v>47</v>
       </c>
       <c r="C447" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D447" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44545,7 +44545,7 @@
         <v>0</v>
       </c>
       <c r="G447" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="448">
@@ -44556,7 +44556,7 @@
         <v>47</v>
       </c>
       <c r="C448" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D448" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44568,7 +44568,7 @@
         <v>0</v>
       </c>
       <c r="G448" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="449">
@@ -44579,7 +44579,7 @@
         <v>47</v>
       </c>
       <c r="C449" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D449" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44591,7 +44591,7 @@
         <v>0</v>
       </c>
       <c r="G449" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="450">
@@ -44602,7 +44602,7 @@
         <v>47</v>
       </c>
       <c r="C450" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D450" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44614,7 +44614,7 @@
         <v>0</v>
       </c>
       <c r="G450" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="451">
@@ -44625,7 +44625,7 @@
         <v>47</v>
       </c>
       <c r="C451" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D451" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44637,7 +44637,7 @@
         <v>0</v>
       </c>
       <c r="G451" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="452">
@@ -44648,7 +44648,7 @@
         <v>47</v>
       </c>
       <c r="C452" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D452" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44660,7 +44660,7 @@
         <v>0</v>
       </c>
       <c r="G452" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="453">
@@ -44671,7 +44671,7 @@
         <v>47</v>
       </c>
       <c r="C453" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D453" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44683,7 +44683,7 @@
         <v>0</v>
       </c>
       <c r="G453" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="454">
@@ -44694,7 +44694,7 @@
         <v>47</v>
       </c>
       <c r="C454" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D454" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44706,7 +44706,7 @@
         <v>0</v>
       </c>
       <c r="G454" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="455">
@@ -44717,7 +44717,7 @@
         <v>47</v>
       </c>
       <c r="C455" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D455" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44729,7 +44729,7 @@
         <v>0</v>
       </c>
       <c r="G455" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="456">
@@ -44740,7 +44740,7 @@
         <v>47</v>
       </c>
       <c r="C456" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D456" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44752,7 +44752,7 @@
         <v>0</v>
       </c>
       <c r="G456" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="457">
@@ -44763,7 +44763,7 @@
         <v>47</v>
       </c>
       <c r="C457" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D457" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44775,7 +44775,7 @@
         <v>0</v>
       </c>
       <c r="G457" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="458">
@@ -44786,7 +44786,7 @@
         <v>47</v>
       </c>
       <c r="C458" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D458" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44798,7 +44798,7 @@
         <v>0</v>
       </c>
       <c r="G458" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="459">
@@ -44809,7 +44809,7 @@
         <v>47</v>
       </c>
       <c r="C459" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D459" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44821,7 +44821,7 @@
         <v>0</v>
       </c>
       <c r="G459" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="460">
@@ -44832,7 +44832,7 @@
         <v>47</v>
       </c>
       <c r="C460" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D460" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44844,7 +44844,7 @@
         <v>0</v>
       </c>
       <c r="G460" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="461">
@@ -44855,7 +44855,7 @@
         <v>47</v>
       </c>
       <c r="C461" s="7" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D461" s="7" t="n">
         <v>0.0139193833879646</v>
@@ -44867,7 +44867,7 @@
         <v>0</v>
       </c>
       <c r="G461" s="7" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
     <row r="462">
@@ -44878,7 +44878,7 @@
         <v>47</v>
       </c>
       <c r="C462" s="11" t="n">
-        <v>0.0516273594070018</v>
+        <v>0.0560684623856515</v>
       </c>
       <c r="D462" s="11" t="n">
         <v>0.0139193833879646</v>
@@ -44890,7 +44890,7 @@
         <v>0</v>
       </c>
       <c r="G462" s="11" t="n">
-        <v>0.0289547553364848</v>
+        <v>0.0286954780378765</v>
       </c>
     </row>
   </sheetData>
